--- a/research/traditional_assets/database/data/denmark/denmark_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_homebuilding.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08760092375001126</v>
+        <v>0.08744330171776125</v>
       </c>
       <c r="C2">
-        <v>241.6578643069425</v>
+        <v>239.7823552325855</v>
       </c>
       <c r="D2">
-        <v>193.2578643069425</v>
+        <v>193.9893552325855</v>
       </c>
       <c r="E2">
-        <v>-82.40000000000001</v>
+        <v>-79.79300000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.607000000000001</v>
       </c>
       <c r="G2">
         <v>48.4</v>
@@ -1445,28 +1445,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1311321</v>
       </c>
       <c r="N2">
-        <v>7.966666666666666</v>
+        <v>7.835534566666666</v>
       </c>
       <c r="O2">
-        <v>1.752666666666667</v>
+        <v>1.723817604666666</v>
       </c>
       <c r="P2">
-        <v>6.214</v>
+        <v>6.111716961999999</v>
       </c>
       <c r="Q2">
-        <v>13.164</v>
+        <v>13.061716962</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08760092375001126</v>
+        <v>0.08793026436137499</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.9729853201241336</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>60.75298623805051</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08744330171776125</v>
+        <v>0.08728567968551121</v>
       </c>
       <c r="C3">
-        <v>239.7823552325855</v>
+        <v>237.9124046587593</v>
       </c>
       <c r="D3">
-        <v>193.9893552325855</v>
+        <v>194.7264046587593</v>
       </c>
       <c r="E3">
-        <v>-79.79300000000001</v>
+        <v>-77.18600000000001</v>
       </c>
       <c r="F3">
-        <v>2.607000000000001</v>
+        <v>5.214000000000001</v>
       </c>
       <c r="G3">
         <v>48.4</v>
@@ -1527,28 +1527,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M3">
-        <v>0.1311321</v>
+        <v>0.2622642000000001</v>
       </c>
       <c r="N3">
-        <v>7.835534566666666</v>
+        <v>7.704402466666666</v>
       </c>
       <c r="O3">
-        <v>1.723817604666666</v>
+        <v>1.694968542666667</v>
       </c>
       <c r="P3">
-        <v>6.111716961999999</v>
+        <v>6.009433924</v>
       </c>
       <c r="Q3">
-        <v>13.061716962</v>
+        <v>12.959433924</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08793026436137499</v>
+        <v>0.08826632620970531</v>
       </c>
       <c r="T3">
-        <v>0.9729853201241336</v>
+        <v>0.9807465637345339</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>60.75298623805051</v>
+        <v>30.37649311902526</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08728567968551121</v>
+        <v>0.08712805765326118</v>
       </c>
       <c r="C4">
-        <v>237.9124046587593</v>
+        <v>236.0480761845438</v>
       </c>
       <c r="D4">
-        <v>194.7264046587593</v>
+        <v>195.4690761845438</v>
       </c>
       <c r="E4">
-        <v>-77.18600000000001</v>
+        <v>-74.57900000000001</v>
       </c>
       <c r="F4">
-        <v>5.214000000000001</v>
+        <v>7.821000000000002</v>
       </c>
       <c r="G4">
         <v>48.4</v>
@@ -1609,28 +1609,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M4">
-        <v>0.2622642000000001</v>
+        <v>0.3933963</v>
       </c>
       <c r="N4">
-        <v>7.704402466666666</v>
+        <v>7.573270366666666</v>
       </c>
       <c r="O4">
-        <v>1.694968542666667</v>
+        <v>1.666119480666667</v>
       </c>
       <c r="P4">
-        <v>6.009433924</v>
+        <v>5.907150885999999</v>
       </c>
       <c r="Q4">
-        <v>12.959433924</v>
+        <v>12.857150886</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08826632620970531</v>
+        <v>0.0886093171683105</v>
       </c>
       <c r="T4">
-        <v>0.9807465637345339</v>
+        <v>0.9886678329863858</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.37649311902526</v>
+        <v>20.25099541268351</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08712805765326118</v>
+        <v>0.08697043562101117</v>
       </c>
       <c r="C5">
-        <v>236.0480761845438</v>
+        <v>234.1894343829816</v>
       </c>
       <c r="D5">
-        <v>195.4690761845438</v>
+        <v>196.2174343829816</v>
       </c>
       <c r="E5">
-        <v>-74.57900000000001</v>
+        <v>-71.97200000000001</v>
       </c>
       <c r="F5">
-        <v>7.821000000000002</v>
+        <v>10.428</v>
       </c>
       <c r="G5">
         <v>48.4</v>
@@ -1691,28 +1691,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M5">
-        <v>0.3933963</v>
+        <v>0.5245284000000001</v>
       </c>
       <c r="N5">
-        <v>7.573270366666666</v>
+        <v>7.442138266666666</v>
       </c>
       <c r="O5">
-        <v>1.666119480666667</v>
+        <v>1.637270418666666</v>
       </c>
       <c r="P5">
-        <v>5.907150885999999</v>
+        <v>5.804867847999999</v>
       </c>
       <c r="Q5">
-        <v>12.857150886</v>
+        <v>12.754867848</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0886093171683105</v>
+        <v>0.08895945377188663</v>
       </c>
       <c r="T5">
-        <v>0.9886678329863858</v>
+        <v>0.9967541286809845</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.25099541268351</v>
+        <v>15.18824655951263</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08697043562101117</v>
+        <v>0.08687131358876114</v>
       </c>
       <c r="C6">
-        <v>234.1894343829816</v>
+        <v>232.0559880426885</v>
       </c>
       <c r="D6">
-        <v>196.2174343829816</v>
+        <v>196.6909880426885</v>
       </c>
       <c r="E6">
-        <v>-71.97200000000001</v>
+        <v>-69.36500000000001</v>
       </c>
       <c r="F6">
-        <v>10.428</v>
+        <v>13.035</v>
       </c>
       <c r="G6">
         <v>48.4</v>
@@ -1773,45 +1773,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M6">
-        <v>0.5245284000000001</v>
+        <v>0.6752130000000002</v>
       </c>
       <c r="N6">
-        <v>7.442138266666666</v>
+        <v>7.291453666666666</v>
       </c>
       <c r="O6">
-        <v>1.637270418666666</v>
+        <v>1.604119806666666</v>
       </c>
       <c r="P6">
-        <v>5.804867847999999</v>
+        <v>5.687333859999999</v>
       </c>
       <c r="Q6">
-        <v>12.754867848</v>
+        <v>12.63733386</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08895945377188663</v>
+        <v>0.08931696167238015</v>
       </c>
       <c r="T6">
-        <v>0.9967541286809845</v>
+        <v>1.00501066217968</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.18824655951263</v>
+        <v>11.79874597596116</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08687131358876114</v>
+        <v>0.0867253915565111</v>
       </c>
       <c r="C7">
-        <v>232.0559880426885</v>
+        <v>230.1503020096135</v>
       </c>
       <c r="D7">
-        <v>196.6909880426885</v>
+        <v>197.3923020096135</v>
       </c>
       <c r="E7">
-        <v>-69.36500000000001</v>
+        <v>-66.758</v>
       </c>
       <c r="F7">
-        <v>13.035</v>
+        <v>15.642</v>
       </c>
       <c r="G7">
         <v>48.4</v>
@@ -1855,28 +1855,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M7">
-        <v>0.6752130000000002</v>
+        <v>0.8102556000000002</v>
       </c>
       <c r="N7">
-        <v>7.291453666666666</v>
+        <v>7.156411066666665</v>
       </c>
       <c r="O7">
-        <v>1.604119806666666</v>
+        <v>1.574410434666666</v>
       </c>
       <c r="P7">
-        <v>5.687333859999999</v>
+        <v>5.582000631999999</v>
       </c>
       <c r="Q7">
-        <v>12.63733386</v>
+        <v>12.532000632</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08931696167238015</v>
+        <v>0.08968207612394799</v>
       </c>
       <c r="T7">
-        <v>1.00501066217968</v>
+        <v>1.01344286660388</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>11.79874597596116</v>
+        <v>9.832288313300968</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0867253915565111</v>
+        <v>0.08667228952426108</v>
       </c>
       <c r="C8">
-        <v>230.1503020096135</v>
+        <v>227.7997577283713</v>
       </c>
       <c r="D8">
-        <v>197.3923020096135</v>
+        <v>197.6487577283713</v>
       </c>
       <c r="E8">
-        <v>-66.75800000000001</v>
+        <v>-64.15100000000001</v>
       </c>
       <c r="F8">
-        <v>15.642</v>
+        <v>18.249</v>
       </c>
       <c r="G8">
         <v>48.4</v>
@@ -1937,45 +1937,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M8">
-        <v>0.8102556000000002</v>
+        <v>0.9763215000000001</v>
       </c>
       <c r="N8">
-        <v>7.156411066666665</v>
+        <v>6.990345166666666</v>
       </c>
       <c r="O8">
-        <v>1.574410434666666</v>
+        <v>1.537875936666667</v>
       </c>
       <c r="P8">
-        <v>5.582000631999999</v>
+        <v>5.452469229999999</v>
       </c>
       <c r="Q8">
-        <v>12.532000632</v>
+        <v>12.40246923</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08968207612394799</v>
+        <v>0.09005504249920546</v>
       </c>
       <c r="T8">
-        <v>1.01344286660388</v>
+        <v>1.022056408757632</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>9.832288313300968</v>
+        <v>8.159880394589964</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08667228952426109</v>
+        <v>0.08658954749201107</v>
       </c>
       <c r="C9">
-        <v>227.7997577283713</v>
+        <v>225.5936903420351</v>
       </c>
       <c r="D9">
-        <v>197.6487577283713</v>
+        <v>198.0496903420351</v>
       </c>
       <c r="E9">
-        <v>-64.151</v>
+        <v>-61.544</v>
       </c>
       <c r="F9">
-        <v>18.24900000000001</v>
+        <v>20.85600000000001</v>
       </c>
       <c r="G9">
         <v>48.4</v>
@@ -2019,45 +2019,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M9">
-        <v>0.9763215000000003</v>
+        <v>1.1324808</v>
       </c>
       <c r="N9">
-        <v>6.990345166666666</v>
+        <v>6.834185866666665</v>
       </c>
       <c r="O9">
-        <v>1.537875936666667</v>
+        <v>1.503520890666666</v>
       </c>
       <c r="P9">
-        <v>5.452469229999999</v>
+        <v>5.330664975999999</v>
       </c>
       <c r="Q9">
-        <v>12.40246923</v>
+        <v>12.280664976</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09005504249920548</v>
+        <v>0.09043611683914246</v>
       </c>
       <c r="T9">
-        <v>1.022056408757632</v>
+        <v>1.03085720182777</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.159880394589962</v>
+        <v>7.034703516975001</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08658954749201107</v>
+        <v>0.08646312545976104</v>
       </c>
       <c r="C10">
-        <v>225.5936903420351</v>
+        <v>223.6024286566983</v>
       </c>
       <c r="D10">
-        <v>198.0496903420351</v>
+        <v>198.6654286566983</v>
       </c>
       <c r="E10">
-        <v>-61.544</v>
+        <v>-58.937</v>
       </c>
       <c r="F10">
-        <v>20.85600000000001</v>
+        <v>23.463</v>
       </c>
       <c r="G10">
         <v>48.4</v>
@@ -2101,28 +2101,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M10">
-        <v>1.1324808</v>
+        <v>1.2740409</v>
       </c>
       <c r="N10">
-        <v>6.834185866666665</v>
+        <v>6.692625766666666</v>
       </c>
       <c r="O10">
-        <v>1.503520890666666</v>
+        <v>1.472377668666667</v>
       </c>
       <c r="P10">
-        <v>5.330664975999999</v>
+        <v>5.220248097999999</v>
       </c>
       <c r="Q10">
-        <v>12.280664976</v>
+        <v>12.170248098</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09043611683914246</v>
+        <v>0.09082556643929784</v>
       </c>
       <c r="T10">
-        <v>1.03085720182777</v>
+        <v>1.039851418921428</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.034703516975001</v>
+        <v>6.253069792866668</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08646312545976104</v>
+        <v>0.08641470342751101</v>
       </c>
       <c r="C11">
-        <v>223.6024286566983</v>
+        <v>221.2322833664846</v>
       </c>
       <c r="D11">
-        <v>198.6654286566983</v>
+        <v>198.9022833664846</v>
       </c>
       <c r="E11">
-        <v>-58.937</v>
+        <v>-56.33</v>
       </c>
       <c r="F11">
-        <v>23.463</v>
+        <v>26.07</v>
       </c>
       <c r="G11">
         <v>48.4</v>
@@ -2183,45 +2183,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M11">
-        <v>1.2740409</v>
+        <v>1.441671</v>
       </c>
       <c r="N11">
-        <v>6.692625766666666</v>
+        <v>6.524995666666666</v>
       </c>
       <c r="O11">
-        <v>1.472377668666667</v>
+        <v>1.435499046666666</v>
       </c>
       <c r="P11">
-        <v>5.220248097999999</v>
+        <v>5.089496619999999</v>
       </c>
       <c r="Q11">
-        <v>12.170248098</v>
+        <v>12.03949662</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09082556643929784</v>
+        <v>0.09122367047501223</v>
       </c>
       <c r="T11">
-        <v>1.039851418921428</v>
+        <v>1.049045507506056</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.253069792866668</v>
+        <v>5.52599495076662</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08641470342751101</v>
+        <v>0.08629608139526099</v>
       </c>
       <c r="C12">
-        <v>221.2322833664846</v>
+        <v>219.2079124075963</v>
       </c>
       <c r="D12">
-        <v>198.9022833664846</v>
+        <v>199.4849124075963</v>
       </c>
       <c r="E12">
-        <v>-56.33</v>
+        <v>-53.723</v>
       </c>
       <c r="F12">
-        <v>26.07000000000001</v>
+        <v>28.67700000000001</v>
       </c>
       <c r="G12">
         <v>48.4</v>
@@ -2265,28 +2265,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M12">
-        <v>1.441671</v>
+        <v>1.5858381</v>
       </c>
       <c r="N12">
-        <v>6.524995666666666</v>
+        <v>6.380828566666666</v>
       </c>
       <c r="O12">
-        <v>1.435499046666666</v>
+        <v>1.403782284666667</v>
       </c>
       <c r="P12">
-        <v>5.089496619999999</v>
+        <v>4.977046281999999</v>
       </c>
       <c r="Q12">
-        <v>12.03949662</v>
+        <v>11.927046282</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09122367047501223</v>
+        <v>0.09163072066883257</v>
       </c>
       <c r="T12">
-        <v>1.049045507506056</v>
+        <v>1.058446204822923</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.52599495076662</v>
+        <v>5.0236317734242</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08629608139526099</v>
+        <v>0.08617745936301097</v>
       </c>
       <c r="C13">
-        <v>219.2079124075963</v>
+        <v>217.1869647765743</v>
       </c>
       <c r="D13">
-        <v>199.4849124075963</v>
+        <v>200.0709647765743</v>
       </c>
       <c r="E13">
-        <v>-53.723</v>
+        <v>-51.116</v>
       </c>
       <c r="F13">
-        <v>28.67700000000001</v>
+        <v>31.28400000000001</v>
       </c>
       <c r="G13">
         <v>48.4</v>
@@ -2347,28 +2347,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M13">
-        <v>1.5858381</v>
+        <v>1.7300052</v>
       </c>
       <c r="N13">
-        <v>6.380828566666666</v>
+        <v>6.236661466666666</v>
       </c>
       <c r="O13">
-        <v>1.403782284666667</v>
+        <v>1.372065522666666</v>
       </c>
       <c r="P13">
-        <v>4.977046281999999</v>
+        <v>4.864595944</v>
       </c>
       <c r="Q13">
-        <v>11.927046282</v>
+        <v>11.814595944</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09163072066883257</v>
+        <v>0.09204702200342155</v>
       </c>
       <c r="T13">
-        <v>1.058446204822923</v>
+        <v>1.068060554351537</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.0236317734242</v>
+        <v>4.604995792305518</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08617745936301097</v>
+        <v>0.08631233733076095</v>
       </c>
       <c r="C14">
-        <v>217.1869647765743</v>
+        <v>213.9138673131146</v>
       </c>
       <c r="D14">
-        <v>200.0709647765743</v>
+        <v>199.4048673131146</v>
       </c>
       <c r="E14">
-        <v>-51.116</v>
+        <v>-48.509</v>
       </c>
       <c r="F14">
-        <v>31.28400000000001</v>
+        <v>33.89100000000001</v>
       </c>
       <c r="G14">
         <v>48.4</v>
@@ -2429,45 +2429,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M14">
-        <v>1.7300052</v>
+        <v>1.9588998</v>
       </c>
       <c r="N14">
-        <v>6.236661466666666</v>
+        <v>6.007766866666666</v>
       </c>
       <c r="O14">
-        <v>1.372065522666666</v>
+        <v>1.321708710666667</v>
       </c>
       <c r="P14">
-        <v>4.864595944</v>
+        <v>4.686058156</v>
       </c>
       <c r="Q14">
-        <v>11.814595944</v>
+        <v>11.636058156</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09204702200342155</v>
+        <v>0.09247289348363327</v>
       </c>
       <c r="T14">
-        <v>1.068060554351537</v>
+        <v>1.077895923409544</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.604995792305518</v>
+        <v>4.066908714098936</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08631233733076095</v>
+        <v>0.08659541529851091</v>
       </c>
       <c r="C15">
-        <v>213.9138673131146</v>
+        <v>209.9232038748236</v>
       </c>
       <c r="D15">
-        <v>199.4048673131146</v>
+        <v>198.0212038748236</v>
       </c>
       <c r="E15">
-        <v>-48.509</v>
+        <v>-45.90199999999999</v>
       </c>
       <c r="F15">
-        <v>33.89100000000001</v>
+        <v>36.49800000000001</v>
       </c>
       <c r="G15">
         <v>48.4</v>
@@ -2511,45 +2511,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M15">
-        <v>1.9588998</v>
+        <v>2.237327400000001</v>
       </c>
       <c r="N15">
-        <v>6.007766866666666</v>
+        <v>5.729339266666665</v>
       </c>
       <c r="O15">
-        <v>1.321708710666667</v>
+        <v>1.260454638666666</v>
       </c>
       <c r="P15">
-        <v>4.686058156</v>
+        <v>4.468884627999999</v>
       </c>
       <c r="Q15">
-        <v>11.636058156</v>
+        <v>11.418884628</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09247289348363327</v>
+        <v>0.09290866895175687</v>
       </c>
       <c r="T15">
-        <v>1.077895923409544</v>
+        <v>1.087960021980528</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.066908714098936</v>
+        <v>3.560796093887137</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08659541529851091</v>
+        <v>0.08685119326626088</v>
       </c>
       <c r="C16">
-        <v>209.9232038748236</v>
+        <v>206.0823917230065</v>
       </c>
       <c r="D16">
-        <v>198.0212038748236</v>
+        <v>196.7873917230065</v>
       </c>
       <c r="E16">
-        <v>-45.90199999999999</v>
+        <v>-43.29499999999999</v>
       </c>
       <c r="F16">
-        <v>36.49800000000001</v>
+        <v>39.10500000000001</v>
       </c>
       <c r="G16">
         <v>48.4</v>
@@ -2593,45 +2593,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M16">
-        <v>2.237327400000001</v>
+        <v>2.506630500000001</v>
       </c>
       <c r="N16">
-        <v>5.729339266666665</v>
+        <v>5.460036166666665</v>
       </c>
       <c r="O16">
-        <v>1.260454638666666</v>
+        <v>1.201207956666666</v>
       </c>
       <c r="P16">
-        <v>4.468884627999999</v>
+        <v>4.258828209999999</v>
       </c>
       <c r="Q16">
-        <v>11.418884628</v>
+        <v>11.20882821</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09290866895175687</v>
+        <v>0.09335469796030693</v>
       </c>
       <c r="T16">
-        <v>1.087960021980528</v>
+        <v>1.09826092287083</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.560796093887137</v>
+        <v>3.178237345578721</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08685119326626088</v>
+        <v>0.08777465123401086</v>
       </c>
       <c r="C17">
-        <v>206.0823917230065</v>
+        <v>199.1459957781487</v>
       </c>
       <c r="D17">
-        <v>196.7873917230065</v>
+        <v>192.4579957781487</v>
       </c>
       <c r="E17">
-        <v>-43.295</v>
+        <v>-40.688</v>
       </c>
       <c r="F17">
-        <v>39.105</v>
+        <v>41.71200000000001</v>
       </c>
       <c r="G17">
         <v>48.4</v>
@@ -2675,45 +2675,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M17">
-        <v>2.5066305</v>
+        <v>2.999092800000001</v>
       </c>
       <c r="N17">
-        <v>5.460036166666665</v>
+        <v>4.967573866666665</v>
       </c>
       <c r="O17">
-        <v>1.201207956666666</v>
+        <v>1.092866250666666</v>
       </c>
       <c r="P17">
-        <v>4.258828209999999</v>
+        <v>3.874707615999999</v>
       </c>
       <c r="Q17">
-        <v>11.20882821</v>
+        <v>10.824707616</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09335469796030693</v>
+        <v>0.0938113467071558</v>
       </c>
       <c r="T17">
-        <v>1.09826092287083</v>
+        <v>1.108807083306139</v>
       </c>
       <c r="U17">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.178237345578722</v>
+        <v>2.656358838468307</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08777465123401086</v>
+        <v>0.08778550920176086</v>
       </c>
       <c r="C18">
-        <v>199.1459957781487</v>
+        <v>196.4892237794016</v>
       </c>
       <c r="D18">
-        <v>192.4579957781487</v>
+        <v>192.4082237794016</v>
       </c>
       <c r="E18">
-        <v>-40.688</v>
+        <v>-38.081</v>
       </c>
       <c r="F18">
-        <v>41.71200000000001</v>
+        <v>44.31900000000001</v>
       </c>
       <c r="G18">
         <v>48.4</v>
@@ -2757,28 +2757,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M18">
-        <v>2.999092800000001</v>
+        <v>3.186536100000001</v>
       </c>
       <c r="N18">
-        <v>4.967573866666665</v>
+        <v>4.780130566666665</v>
       </c>
       <c r="O18">
-        <v>1.092866250666666</v>
+        <v>1.051628724666666</v>
       </c>
       <c r="P18">
-        <v>3.874707615999999</v>
+        <v>3.728501841999999</v>
       </c>
       <c r="Q18">
-        <v>10.824707616</v>
+        <v>10.678501842</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0938113467071558</v>
+        <v>0.09427899903826609</v>
       </c>
       <c r="T18">
-        <v>1.108807083306139</v>
+        <v>1.119607368089286</v>
       </c>
       <c r="U18">
         <v>0.07190000000000001</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.656358838468307</v>
+        <v>2.500102436205466</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08778550920176086</v>
+        <v>0.08834392716951081</v>
       </c>
       <c r="C19">
-        <v>196.4892237794016</v>
+        <v>191.3567350328368</v>
       </c>
       <c r="D19">
-        <v>192.4082237794016</v>
+        <v>189.8827350328368</v>
       </c>
       <c r="E19">
-        <v>-38.081</v>
+        <v>-35.47399999999999</v>
       </c>
       <c r="F19">
-        <v>44.31900000000001</v>
+        <v>46.92600000000002</v>
       </c>
       <c r="G19">
         <v>48.4</v>
@@ -2839,45 +2839,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M19">
-        <v>3.186536100000001</v>
+        <v>3.556990800000002</v>
       </c>
       <c r="N19">
-        <v>4.780130566666665</v>
+        <v>4.409675866666664</v>
       </c>
       <c r="O19">
-        <v>1.051628724666666</v>
+        <v>0.9701286906666661</v>
       </c>
       <c r="P19">
-        <v>3.728501841999999</v>
+        <v>3.439547175999998</v>
       </c>
       <c r="Q19">
-        <v>10.678501842</v>
+        <v>10.389547176</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09427899903826609</v>
+        <v>0.09475805752379368</v>
       </c>
       <c r="T19">
-        <v>1.119607368089286</v>
+        <v>1.13067107445251</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.500102436205466</v>
+        <v>2.239720908658707</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08834392716951082</v>
+        <v>0.08838520513726079</v>
       </c>
       <c r="C20">
-        <v>191.3567350328367</v>
+        <v>188.5656811252015</v>
       </c>
       <c r="D20">
-        <v>189.8827350328367</v>
+        <v>189.6986811252015</v>
       </c>
       <c r="E20">
-        <v>-35.474</v>
+        <v>-32.867</v>
       </c>
       <c r="F20">
-        <v>46.92600000000001</v>
+        <v>49.53300000000001</v>
       </c>
       <c r="G20">
         <v>48.4</v>
@@ -2921,28 +2921,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M20">
-        <v>3.556990800000001</v>
+        <v>3.754601400000001</v>
       </c>
       <c r="N20">
-        <v>4.409675866666666</v>
+        <v>4.212065266666665</v>
       </c>
       <c r="O20">
-        <v>0.9701286906666664</v>
+        <v>0.9266543586666662</v>
       </c>
       <c r="P20">
-        <v>3.439547175999999</v>
+        <v>3.285410907999998</v>
       </c>
       <c r="Q20">
-        <v>10.389547176</v>
+        <v>10.235410908</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09475805752379368</v>
+        <v>0.09524894461390221</v>
       </c>
       <c r="T20">
-        <v>1.13067107445251</v>
+        <v>1.142007958750628</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.239720908658708</v>
+        <v>2.121840860834565</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08838520513726079</v>
+        <v>0.08842648310501078</v>
       </c>
       <c r="C21">
-        <v>188.5656811252015</v>
+        <v>185.7749836800613</v>
       </c>
       <c r="D21">
-        <v>189.6986811252015</v>
+        <v>189.5149836800613</v>
       </c>
       <c r="E21">
-        <v>-32.867</v>
+        <v>-30.25999999999999</v>
       </c>
       <c r="F21">
-        <v>49.53300000000001</v>
+        <v>52.14000000000001</v>
       </c>
       <c r="G21">
         <v>48.4</v>
@@ -3003,28 +3003,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M21">
-        <v>3.754601400000001</v>
+        <v>3.952212000000002</v>
       </c>
       <c r="N21">
-        <v>4.212065266666665</v>
+        <v>4.014454666666664</v>
       </c>
       <c r="O21">
-        <v>0.9266543586666662</v>
+        <v>0.8831800266666661</v>
       </c>
       <c r="P21">
-        <v>3.285410907999998</v>
+        <v>3.131274639999998</v>
       </c>
       <c r="Q21">
-        <v>10.235410908</v>
+        <v>10.08127464</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09524894461390221</v>
+        <v>0.09575210388126346</v>
       </c>
       <c r="T21">
-        <v>1.142007958750628</v>
+        <v>1.1536282651562</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.121840860834565</v>
+        <v>2.015748817792836</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08842648310501078</v>
+        <v>0.09079372107276075</v>
       </c>
       <c r="C22">
-        <v>185.7749836800613</v>
+        <v>173.1971020963961</v>
       </c>
       <c r="D22">
-        <v>189.5149836800613</v>
+        <v>179.5441020963961</v>
       </c>
       <c r="E22">
-        <v>-30.25999999999999</v>
+        <v>-27.65299999999999</v>
       </c>
       <c r="F22">
-        <v>52.14000000000001</v>
+        <v>54.74700000000001</v>
       </c>
       <c r="G22">
         <v>48.4</v>
@@ -3085,45 +3085,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M22">
-        <v>3.952212000000002</v>
+        <v>4.927230000000001</v>
       </c>
       <c r="N22">
-        <v>4.014454666666664</v>
+        <v>3.039436666666665</v>
       </c>
       <c r="O22">
-        <v>0.8831800266666661</v>
+        <v>0.6686760666666663</v>
       </c>
       <c r="P22">
-        <v>3.131274639999998</v>
+        <v>2.370760599999999</v>
       </c>
       <c r="Q22">
-        <v>10.08127464</v>
+        <v>9.3207606</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09575210388126346</v>
+        <v>0.09626800135792499</v>
       </c>
       <c r="T22">
-        <v>1.1536282651562</v>
+        <v>1.165542756534065</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.015748817792836</v>
+        <v>1.616865189298382</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09079372107276075</v>
+        <v>0.09094575904051072</v>
       </c>
       <c r="C23">
-        <v>173.1971020963961</v>
+        <v>169.9854490573425</v>
       </c>
       <c r="D23">
-        <v>179.5441020963961</v>
+        <v>178.9394490573425</v>
       </c>
       <c r="E23">
-        <v>-27.653</v>
+        <v>-25.04599999999999</v>
       </c>
       <c r="F23">
-        <v>54.74700000000001</v>
+        <v>57.35400000000001</v>
       </c>
       <c r="G23">
         <v>48.4</v>
@@ -3167,28 +3167,28 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M23">
-        <v>4.927230000000001</v>
+        <v>5.161860000000001</v>
       </c>
       <c r="N23">
-        <v>3.039436666666665</v>
+        <v>2.804806666666665</v>
       </c>
       <c r="O23">
-        <v>0.6686760666666663</v>
+        <v>0.6170574666666663</v>
       </c>
       <c r="P23">
-        <v>2.370760599999999</v>
+        <v>2.187749199999999</v>
       </c>
       <c r="Q23">
-        <v>9.3207606</v>
+        <v>9.137749199999998</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09626800135792499</v>
+        <v>0.09679712697501375</v>
       </c>
       <c r="T23">
-        <v>1.165542756534064</v>
+        <v>1.177762747690849</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.616865189298382</v>
+        <v>1.543371317057546</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09094575904051072</v>
+        <v>0.1021936624999293</v>
       </c>
       <c r="C24">
-        <v>169.9854490573425</v>
+        <v>131.688381080625</v>
       </c>
       <c r="D24">
-        <v>178.9394490573425</v>
+        <v>143.249381080625</v>
       </c>
       <c r="E24">
-        <v>-25.04599999999999</v>
+        <v>-22.43899999999999</v>
       </c>
       <c r="F24">
-        <v>57.35400000000001</v>
+        <v>59.96100000000001</v>
       </c>
       <c r="G24">
         <v>48.4</v>
@@ -3249,45 +3249,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M24">
-        <v>5.161860000000001</v>
+        <v>8.802274800000003</v>
       </c>
       <c r="N24">
-        <v>2.804806666666665</v>
+        <v>-0.8356081333333369</v>
       </c>
       <c r="O24">
-        <v>0.6170574666666663</v>
+        <v>-0.1838337893333341</v>
       </c>
       <c r="P24">
-        <v>2.187749199999999</v>
+        <v>-0.6517743440000028</v>
       </c>
       <c r="Q24">
-        <v>9.137749199999998</v>
+        <v>6.298225655999998</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09679712697501375</v>
+        <v>0.09760076358056101</v>
       </c>
       <c r="T24">
-        <v>1.177762747690849</v>
+        <v>1.196322484539515</v>
       </c>
       <c r="U24">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.22</v>
+        <v>0.1991151953886586</v>
       </c>
       <c r="W24">
-        <v>0.0702</v>
+        <v>0.1175698893169449</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.543371317057546</v>
+        <v>0.9050690699484483</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1021936624999293</v>
+        <v>0.1032036624999293</v>
       </c>
       <c r="C25">
-        <v>131.688381080625</v>
+        <v>126.5609517457962</v>
       </c>
       <c r="D25">
-        <v>143.249381080625</v>
+        <v>140.7289517457962</v>
       </c>
       <c r="E25">
-        <v>-22.43899999999999</v>
+        <v>-19.83199999999999</v>
       </c>
       <c r="F25">
-        <v>59.96100000000001</v>
+        <v>62.56800000000002</v>
       </c>
       <c r="G25">
         <v>48.4</v>
@@ -3331,37 +3331,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M25">
-        <v>8.802274800000003</v>
+        <v>9.184982400000004</v>
       </c>
       <c r="N25">
-        <v>-0.8356081333333369</v>
+        <v>-1.218315733333339</v>
       </c>
       <c r="O25">
-        <v>-0.1838337893333341</v>
+        <v>-0.2680294613333345</v>
       </c>
       <c r="P25">
-        <v>-0.6517743440000028</v>
+        <v>-0.950286272000004</v>
       </c>
       <c r="Q25">
-        <v>6.298225655999998</v>
+        <v>5.999713727999996</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09760076358056101</v>
+        <v>0.09828235257504209</v>
       </c>
       <c r="T25">
-        <v>1.196322484539515</v>
+        <v>1.212063569862404</v>
       </c>
       <c r="U25">
         <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.1991151953886586</v>
+        <v>0.1908187289141312</v>
       </c>
       <c r="W25">
-        <v>0.1175698893169449</v>
+        <v>0.1187878105954056</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9050690699484483</v>
+        <v>0.8673578587005961</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1032036624999293</v>
+        <v>0.1042136624999293</v>
       </c>
       <c r="C26">
-        <v>126.5609517457962</v>
+        <v>121.5206812542665</v>
       </c>
       <c r="D26">
-        <v>140.7289517457963</v>
+        <v>138.2956812542666</v>
       </c>
       <c r="E26">
-        <v>-19.83199999999999</v>
+        <v>-17.22499999999999</v>
       </c>
       <c r="F26">
-        <v>62.56800000000001</v>
+        <v>65.17500000000001</v>
       </c>
       <c r="G26">
         <v>48.4</v>
@@ -3413,37 +3413,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M26">
-        <v>9.184982400000003</v>
+        <v>9.567690000000002</v>
       </c>
       <c r="N26">
-        <v>-1.218315733333337</v>
+        <v>-1.601023333333337</v>
       </c>
       <c r="O26">
-        <v>-0.2680294613333341</v>
+        <v>-0.3522251333333341</v>
       </c>
       <c r="P26">
-        <v>-0.9502862720000027</v>
+        <v>-1.248798200000003</v>
       </c>
       <c r="Q26">
-        <v>5.999713727999998</v>
+        <v>5.701201799999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09828235257504207</v>
+        <v>0.09898211727604264</v>
       </c>
       <c r="T26">
-        <v>1.212063569862404</v>
+        <v>1.228224417460569</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.1908187289141312</v>
+        <v>0.1831859797575659</v>
       </c>
       <c r="W26">
-        <v>0.1187878105954056</v>
+        <v>0.1199082981715893</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8673578587005962</v>
+        <v>0.8326635443525725</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1042136624999293</v>
+        <v>0.1052236624999293</v>
       </c>
       <c r="C27">
-        <v>121.5206812542665</v>
+        <v>116.5631253950248</v>
       </c>
       <c r="D27">
-        <v>138.2956812542666</v>
+        <v>135.9451253950248</v>
       </c>
       <c r="E27">
-        <v>-17.22499999999999</v>
+        <v>-14.61799999999999</v>
       </c>
       <c r="F27">
-        <v>65.17500000000001</v>
+        <v>67.78200000000001</v>
       </c>
       <c r="G27">
         <v>48.4</v>
@@ -3495,37 +3495,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M27">
-        <v>9.567690000000002</v>
+        <v>9.950397600000002</v>
       </c>
       <c r="N27">
-        <v>-1.601023333333337</v>
+        <v>-1.983730933333336</v>
       </c>
       <c r="O27">
-        <v>-0.3522251333333341</v>
+        <v>-0.436420805333334</v>
       </c>
       <c r="P27">
-        <v>-1.248798200000003</v>
+        <v>-1.547310128000002</v>
       </c>
       <c r="Q27">
-        <v>5.701201799999998</v>
+        <v>5.402689871999998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09898211727604264</v>
+        <v>0.0997007945365297</v>
       </c>
       <c r="T27">
-        <v>1.228224417460569</v>
+        <v>1.24482204472355</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1831859797575659</v>
+        <v>0.1761403651515057</v>
       </c>
       <c r="W27">
-        <v>0.1199082981715893</v>
+        <v>0.120942594395759</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8326635443525725</v>
+        <v>0.800638023415935</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1052236624999293</v>
+        <v>0.12132847391836</v>
       </c>
       <c r="C28">
-        <v>116.5631253950248</v>
+        <v>84.96877143222247</v>
       </c>
       <c r="D28">
-        <v>135.9451253950248</v>
+        <v>106.9577714322225</v>
       </c>
       <c r="E28">
-        <v>-14.61799999999999</v>
+        <v>-12.011</v>
       </c>
       <c r="F28">
-        <v>67.78200000000001</v>
+        <v>70.38900000000001</v>
       </c>
       <c r="G28">
         <v>48.4</v>
@@ -3577,45 +3577,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M28">
-        <v>9.950397600000002</v>
+        <v>14.1341112</v>
       </c>
       <c r="N28">
-        <v>-1.983730933333336</v>
+        <v>-6.167444533333337</v>
       </c>
       <c r="O28">
-        <v>-0.436420805333334</v>
+        <v>-1.356837797333334</v>
       </c>
       <c r="P28">
-        <v>-1.547310128000002</v>
+        <v>-4.810606736000003</v>
       </c>
       <c r="Q28">
-        <v>5.402689871999998</v>
+        <v>2.139393263999997</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0997007945365297</v>
+        <v>0.1011443827061132</v>
       </c>
       <c r="T28">
-        <v>1.24482204472355</v>
+        <v>1.278161263420629</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1761403651515057</v>
+        <v>0.1240026091394177</v>
       </c>
       <c r="W28">
-        <v>0.120942594395759</v>
+        <v>0.1759002760848049</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.800638023415935</v>
+        <v>0.5636482233609896</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.12132847391836</v>
+        <v>0.12287847391836</v>
       </c>
       <c r="C29">
-        <v>84.96877143222247</v>
+        <v>80.21091740914535</v>
       </c>
       <c r="D29">
-        <v>106.9577714322225</v>
+        <v>104.8069174091454</v>
       </c>
       <c r="E29">
-        <v>-12.011</v>
+        <v>-9.403999999999982</v>
       </c>
       <c r="F29">
-        <v>70.38900000000001</v>
+        <v>72.99600000000002</v>
       </c>
       <c r="G29">
         <v>48.4</v>
@@ -3659,37 +3659,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M29">
-        <v>14.1341112</v>
+        <v>14.65759680000001</v>
       </c>
       <c r="N29">
-        <v>-6.167444533333337</v>
+        <v>-6.69093013333334</v>
       </c>
       <c r="O29">
-        <v>-1.356837797333334</v>
+        <v>-1.472004629333335</v>
       </c>
       <c r="P29">
-        <v>-4.810606736000003</v>
+        <v>-5.218925504000005</v>
       </c>
       <c r="Q29">
-        <v>2.139393263999997</v>
+        <v>1.731074495999995</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1011443827061132</v>
+        <v>0.1019130546881426</v>
       </c>
       <c r="T29">
-        <v>1.278161263420629</v>
+        <v>1.29591350319036</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1240026091394177</v>
+        <v>0.1195739445272956</v>
       </c>
       <c r="W29">
-        <v>0.1759002760848049</v>
+        <v>0.176789551938919</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5636482233609896</v>
+        <v>0.5435179296695256</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.12287847391836</v>
+        <v>0.12442847391836</v>
       </c>
       <c r="C30">
-        <v>80.21091740914535</v>
+        <v>75.53786278683584</v>
       </c>
       <c r="D30">
-        <v>104.8069174091454</v>
+        <v>102.7408627868359</v>
       </c>
       <c r="E30">
-        <v>-9.403999999999982</v>
+        <v>-6.796999999999983</v>
       </c>
       <c r="F30">
-        <v>72.99600000000002</v>
+        <v>75.60300000000002</v>
       </c>
       <c r="G30">
         <v>48.4</v>
@@ -3741,37 +3741,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M30">
-        <v>14.65759680000001</v>
+        <v>15.1810824</v>
       </c>
       <c r="N30">
-        <v>-6.69093013333334</v>
+        <v>-7.214415733333339</v>
       </c>
       <c r="O30">
-        <v>-1.472004629333335</v>
+        <v>-1.587171461333335</v>
       </c>
       <c r="P30">
-        <v>-5.218925504000005</v>
+        <v>-5.627244272000004</v>
       </c>
       <c r="Q30">
-        <v>1.731074495999995</v>
+        <v>1.322755727999996</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1019130546881426</v>
+        <v>0.1027033794020601</v>
       </c>
       <c r="T30">
-        <v>1.29591350319036</v>
+        <v>1.314165806052196</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1195739445272956</v>
+        <v>0.1154507050608372</v>
       </c>
       <c r="W30">
-        <v>0.176789551938919</v>
+        <v>0.1776174984237839</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5435179296695256</v>
+        <v>0.5247759320947143</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.12442847391836</v>
+        <v>0.12597847391836</v>
       </c>
       <c r="C31">
-        <v>75.53786278683586</v>
+        <v>70.94468957179379</v>
       </c>
       <c r="D31">
-        <v>102.7408627868359</v>
+        <v>100.7546895717938</v>
       </c>
       <c r="E31">
-        <v>-6.796999999999997</v>
+        <v>-4.189999999999998</v>
       </c>
       <c r="F31">
-        <v>75.60300000000001</v>
+        <v>78.21000000000001</v>
       </c>
       <c r="G31">
         <v>48.4</v>
@@ -3823,37 +3823,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M31">
-        <v>15.1810824</v>
+        <v>15.704568</v>
       </c>
       <c r="N31">
-        <v>-7.214415733333337</v>
+        <v>-7.737901333333336</v>
       </c>
       <c r="O31">
-        <v>-1.587171461333334</v>
+        <v>-1.702338293333334</v>
       </c>
       <c r="P31">
-        <v>-5.627244272000003</v>
+        <v>-6.035563040000002</v>
       </c>
       <c r="Q31">
-        <v>1.322755727999997</v>
+        <v>0.914436959999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1027033794020601</v>
+        <v>0.1035162848220895</v>
       </c>
       <c r="T31">
-        <v>1.314165806052196</v>
+        <v>1.332939603281513</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1154507050608372</v>
+        <v>0.1116023482254759</v>
       </c>
       <c r="W31">
-        <v>0.1776174984237839</v>
+        <v>0.1783902484763244</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5247759320947145</v>
+        <v>0.5072834010248907</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.12597847391836</v>
+        <v>0.1385862065439291</v>
       </c>
       <c r="C32">
-        <v>70.94468957179379</v>
+        <v>54.64720437783359</v>
       </c>
       <c r="D32">
-        <v>100.7546895717938</v>
+        <v>87.0642043778336</v>
       </c>
       <c r="E32">
-        <v>-4.189999999999998</v>
+        <v>-1.582999999999998</v>
       </c>
       <c r="F32">
-        <v>78.21000000000001</v>
+        <v>80.81700000000001</v>
       </c>
       <c r="G32">
         <v>48.4</v>
@@ -3905,45 +3905,45 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M32">
-        <v>15.704568</v>
+        <v>19.0566486</v>
       </c>
       <c r="N32">
-        <v>-7.737901333333336</v>
+        <v>-11.08998193333334</v>
       </c>
       <c r="O32">
-        <v>-1.702338293333334</v>
+        <v>-2.439796025333334</v>
       </c>
       <c r="P32">
-        <v>-6.035563040000002</v>
+        <v>-8.650185908000003</v>
       </c>
       <c r="Q32">
-        <v>0.914436959999998</v>
+        <v>-1.700185908000003</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1035162848220895</v>
+        <v>0.104653814494249</v>
       </c>
       <c r="T32">
-        <v>1.332939603281513</v>
+        <v>1.359210496402979</v>
       </c>
       <c r="U32">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1116023482254759</v>
+        <v>0.09197140081948441</v>
       </c>
       <c r="W32">
-        <v>0.1783902484763244</v>
+        <v>0.2141131436867656</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.5072834010248907</v>
+        <v>0.4180518219067473</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1385862065439291</v>
+        <v>0.1404862065439291</v>
       </c>
       <c r="C33">
-        <v>54.64720437783359</v>
+        <v>50.29314961288067</v>
       </c>
       <c r="D33">
-        <v>87.0642043778336</v>
+        <v>85.3171496128807</v>
       </c>
       <c r="E33">
-        <v>-1.582999999999998</v>
+        <v>1.024000000000015</v>
       </c>
       <c r="F33">
-        <v>80.81700000000001</v>
+        <v>83.42400000000002</v>
       </c>
       <c r="G33">
         <v>48.4</v>
@@ -3987,37 +3987,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M33">
-        <v>19.0566486</v>
+        <v>19.6713792</v>
       </c>
       <c r="N33">
-        <v>-11.08998193333334</v>
+        <v>-11.70471253333334</v>
       </c>
       <c r="O33">
-        <v>-2.439796025333334</v>
+        <v>-2.575036757333335</v>
       </c>
       <c r="P33">
-        <v>-8.650185908000003</v>
+        <v>-9.129675776000004</v>
       </c>
       <c r="Q33">
-        <v>-1.700185908000003</v>
+        <v>-2.179675776000004</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.104653814494249</v>
+        <v>0.1055193117662232</v>
       </c>
       <c r="T33">
-        <v>1.359210496402979</v>
+        <v>1.379198886055964</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.09197140081948441</v>
+        <v>0.08909729454387551</v>
       </c>
       <c r="W33">
-        <v>0.2141131436867656</v>
+        <v>0.2147908579465542</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.4180518219067473</v>
+        <v>0.4049877024721613</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1404862065439291</v>
+        <v>0.1423862065439291</v>
       </c>
       <c r="C34">
-        <v>50.29314961288067</v>
+        <v>46.00782938409371</v>
       </c>
       <c r="D34">
-        <v>85.3171496128807</v>
+        <v>83.63882938409374</v>
       </c>
       <c r="E34">
-        <v>1.024000000000015</v>
+        <v>3.631000000000014</v>
       </c>
       <c r="F34">
-        <v>83.42400000000002</v>
+        <v>86.03100000000002</v>
       </c>
       <c r="G34">
         <v>48.4</v>
@@ -4069,37 +4069,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M34">
-        <v>19.6713792</v>
+        <v>20.28610980000001</v>
       </c>
       <c r="N34">
-        <v>-11.70471253333334</v>
+        <v>-12.31944313333334</v>
       </c>
       <c r="O34">
-        <v>-2.575036757333335</v>
+        <v>-2.710277489333335</v>
       </c>
       <c r="P34">
-        <v>-9.129675776000004</v>
+        <v>-9.609165644000006</v>
       </c>
       <c r="Q34">
-        <v>-2.179675776000004</v>
+        <v>-2.659165644000006</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1055193117662232</v>
+        <v>0.1064106447776594</v>
       </c>
       <c r="T34">
-        <v>1.379198886055964</v>
+        <v>1.399783944056799</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08909729454387551</v>
+        <v>0.08639737652739443</v>
       </c>
       <c r="W34">
-        <v>0.2147908579465542</v>
+        <v>0.2154274986148404</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4049877024721613</v>
+        <v>0.3927153478517929</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1423862065439291</v>
+        <v>0.1442862065439292</v>
       </c>
       <c r="C35">
-        <v>46.00782938409371</v>
+        <v>41.78726560286616</v>
       </c>
       <c r="D35">
-        <v>83.63882938409374</v>
+        <v>82.02526560286617</v>
       </c>
       <c r="E35">
-        <v>3.631000000000014</v>
+        <v>6.238000000000014</v>
       </c>
       <c r="F35">
-        <v>86.03100000000002</v>
+        <v>88.63800000000002</v>
       </c>
       <c r="G35">
         <v>48.4</v>
@@ -4151,37 +4151,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M35">
-        <v>20.28610980000001</v>
+        <v>20.90084040000001</v>
       </c>
       <c r="N35">
-        <v>-12.31944313333334</v>
+        <v>-12.93417373333334</v>
       </c>
       <c r="O35">
-        <v>-2.710277489333335</v>
+        <v>-2.845518221333335</v>
       </c>
       <c r="P35">
-        <v>-9.609165644000006</v>
+        <v>-10.08865551200001</v>
       </c>
       <c r="Q35">
-        <v>-2.659165644000006</v>
+        <v>-3.138655512000006</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1064106447776594</v>
+        <v>0.1073289878803512</v>
       </c>
       <c r="T35">
-        <v>1.399783944056799</v>
+        <v>1.420992791694023</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.08639737652739443</v>
+        <v>0.08385627721776517</v>
       </c>
       <c r="W35">
-        <v>0.2154274986148404</v>
+        <v>0.216026689832051</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3927153478517929</v>
+        <v>0.3811648964443871</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1442862065439292</v>
+        <v>0.1461862065439291</v>
       </c>
       <c r="C36">
-        <v>41.78726560286616</v>
+        <v>37.62778135218134</v>
       </c>
       <c r="D36">
-        <v>82.02526560286617</v>
+        <v>80.47278135218137</v>
       </c>
       <c r="E36">
-        <v>6.238000000000014</v>
+        <v>8.845000000000013</v>
       </c>
       <c r="F36">
-        <v>88.63800000000002</v>
+        <v>91.24500000000002</v>
       </c>
       <c r="G36">
         <v>48.4</v>
@@ -4233,37 +4233,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M36">
-        <v>20.90084040000001</v>
+        <v>21.515571</v>
       </c>
       <c r="N36">
-        <v>-12.93417373333334</v>
+        <v>-13.54890433333334</v>
       </c>
       <c r="O36">
-        <v>-2.845518221333335</v>
+        <v>-2.980758953333335</v>
       </c>
       <c r="P36">
-        <v>-10.08865551200001</v>
+        <v>-10.56814538</v>
       </c>
       <c r="Q36">
-        <v>-3.138655512000006</v>
+        <v>-3.618145380000004</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1073289878803512</v>
+        <v>0.1082755876938951</v>
       </c>
       <c r="T36">
-        <v>1.420992791694023</v>
+        <v>1.442854219258547</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.08385627721776517</v>
+        <v>0.08146038358297189</v>
       </c>
       <c r="W36">
-        <v>0.216026689832051</v>
+        <v>0.2165916415511352</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3811648964443871</v>
+        <v>0.3702744708316904</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1461862065439291</v>
+        <v>0.1480862065439291</v>
       </c>
       <c r="C37">
-        <v>37.62778135218134</v>
+        <v>33.52597291480438</v>
       </c>
       <c r="D37">
-        <v>80.47278135218137</v>
+        <v>78.97797291480443</v>
       </c>
       <c r="E37">
-        <v>8.845000000000013</v>
+        <v>11.45200000000003</v>
       </c>
       <c r="F37">
-        <v>91.24500000000002</v>
+        <v>93.85200000000003</v>
       </c>
       <c r="G37">
         <v>48.4</v>
@@ -4315,37 +4315,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M37">
-        <v>21.515571</v>
+        <v>22.13030160000001</v>
       </c>
       <c r="N37">
-        <v>-13.54890433333334</v>
+        <v>-14.16363493333334</v>
       </c>
       <c r="O37">
-        <v>-2.980758953333335</v>
+        <v>-3.115999685333336</v>
       </c>
       <c r="P37">
-        <v>-10.56814538</v>
+        <v>-11.04763524800001</v>
       </c>
       <c r="Q37">
-        <v>-3.618145380000004</v>
+        <v>-4.097635248000009</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1082755876938951</v>
+        <v>0.1092517687516122</v>
       </c>
       <c r="T37">
-        <v>1.442854219258547</v>
+        <v>1.465398816434462</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.08146038358297189</v>
+        <v>0.07919759515011154</v>
       </c>
       <c r="W37">
-        <v>0.2165916415511352</v>
+        <v>0.2171252070636037</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3702744708316904</v>
+        <v>0.3599890688641434</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1480862065439291</v>
+        <v>0.1499862065439291</v>
       </c>
       <c r="C38">
-        <v>33.5259729148044</v>
+        <v>29.47868486213541</v>
       </c>
       <c r="D38">
-        <v>78.97797291480443</v>
+        <v>77.53768486213542</v>
       </c>
       <c r="E38">
-        <v>11.45200000000001</v>
+        <v>14.05900000000001</v>
       </c>
       <c r="F38">
-        <v>93.85200000000002</v>
+        <v>96.45900000000002</v>
       </c>
       <c r="G38">
         <v>48.4</v>
@@ -4397,37 +4397,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M38">
-        <v>22.13030160000001</v>
+        <v>22.7450322</v>
       </c>
       <c r="N38">
-        <v>-14.16363493333334</v>
+        <v>-14.77836553333334</v>
       </c>
       <c r="O38">
-        <v>-3.115999685333335</v>
+        <v>-3.251240417333335</v>
       </c>
       <c r="P38">
-        <v>-11.04763524800001</v>
+        <v>-11.527125116</v>
       </c>
       <c r="Q38">
-        <v>-4.097635248000006</v>
+        <v>-4.577125116000004</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1092517687516122</v>
+        <v>0.1102589396841774</v>
       </c>
       <c r="T38">
-        <v>1.465398816434462</v>
+        <v>1.488659115108024</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07919759515011156</v>
+        <v>0.07705711960551395</v>
       </c>
       <c r="W38">
-        <v>0.2171252070636037</v>
+        <v>0.2176299311970198</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3599890688641434</v>
+        <v>0.3502596345705179</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1499862065439291</v>
+        <v>0.1518862065439291</v>
       </c>
       <c r="C39">
-        <v>29.47868486213541</v>
+        <v>25.48298782000809</v>
       </c>
       <c r="D39">
-        <v>77.53768486213542</v>
+        <v>76.14898782000812</v>
       </c>
       <c r="E39">
-        <v>14.05900000000001</v>
+        <v>16.66600000000001</v>
       </c>
       <c r="F39">
-        <v>96.45900000000002</v>
+        <v>99.06600000000002</v>
       </c>
       <c r="G39">
         <v>48.4</v>
@@ -4479,37 +4479,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M39">
-        <v>22.7450322</v>
+        <v>23.35976280000001</v>
       </c>
       <c r="N39">
-        <v>-14.77836553333334</v>
+        <v>-15.39309613333334</v>
       </c>
       <c r="O39">
-        <v>-3.251240417333335</v>
+        <v>-3.386481149333335</v>
       </c>
       <c r="P39">
-        <v>-11.527125116</v>
+        <v>-12.00661498400001</v>
       </c>
       <c r="Q39">
-        <v>-4.577125116000004</v>
+        <v>-5.056614984000006</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1102589396841774</v>
+        <v>0.1112986000016642</v>
       </c>
       <c r="T39">
-        <v>1.488659115108024</v>
+        <v>1.512669745996863</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.07705711960551395</v>
+        <v>0.07502930066852674</v>
       </c>
       <c r="W39">
-        <v>0.2176299311970198</v>
+        <v>0.2181080909023614</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3502596345705179</v>
+        <v>0.3410422757660306</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1518862065439291</v>
+        <v>0.1537862065439291</v>
       </c>
       <c r="C40">
-        <v>25.48298782000809</v>
+        <v>21.53615858173261</v>
       </c>
       <c r="D40">
-        <v>76.14898782000812</v>
+        <v>74.80915858173263</v>
       </c>
       <c r="E40">
-        <v>16.66600000000001</v>
+        <v>19.27300000000001</v>
       </c>
       <c r="F40">
-        <v>99.06600000000002</v>
+        <v>101.673</v>
       </c>
       <c r="G40">
         <v>48.4</v>
@@ -4561,37 +4561,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M40">
-        <v>23.35976280000001</v>
+        <v>23.9744934</v>
       </c>
       <c r="N40">
-        <v>-15.39309613333334</v>
+        <v>-16.00782673333334</v>
       </c>
       <c r="O40">
-        <v>-3.386481149333335</v>
+        <v>-3.521721881333335</v>
       </c>
       <c r="P40">
-        <v>-12.00661498400001</v>
+        <v>-12.486104852</v>
       </c>
       <c r="Q40">
-        <v>-5.056614984000006</v>
+        <v>-5.536104852000004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1112986000016642</v>
+        <v>0.1123723475426751</v>
       </c>
       <c r="T40">
-        <v>1.512669745996863</v>
+        <v>1.537467610685336</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.07502930066852674</v>
+        <v>0.07310547244625684</v>
       </c>
       <c r="W40">
-        <v>0.2181080909023614</v>
+        <v>0.2185617295971726</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3410422757660306</v>
+        <v>0.3322976020284401</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1537862065439291</v>
+        <v>0.1556862065439291</v>
       </c>
       <c r="C41">
-        <v>21.53615858173261</v>
+        <v>17.63566228428354</v>
       </c>
       <c r="D41">
-        <v>74.80915858173263</v>
+        <v>73.51566228428358</v>
       </c>
       <c r="E41">
-        <v>19.27300000000001</v>
+        <v>21.88000000000002</v>
       </c>
       <c r="F41">
-        <v>101.673</v>
+        <v>104.28</v>
       </c>
       <c r="G41">
         <v>48.4</v>
@@ -4643,37 +4643,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M41">
-        <v>23.9744934</v>
+        <v>24.58922400000001</v>
       </c>
       <c r="N41">
-        <v>-16.00782673333334</v>
+        <v>-16.62255733333334</v>
       </c>
       <c r="O41">
-        <v>-3.521721881333335</v>
+        <v>-3.656962613333336</v>
       </c>
       <c r="P41">
-        <v>-12.486104852</v>
+        <v>-12.96559472000001</v>
       </c>
       <c r="Q41">
-        <v>-5.536104852000004</v>
+        <v>-6.015594720000007</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1123723475426751</v>
+        <v>0.1134818866683863</v>
       </c>
       <c r="T41">
-        <v>1.537467610685336</v>
+        <v>1.563092070863426</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.07310547244625684</v>
+        <v>0.0712778356351004</v>
       </c>
       <c r="W41">
-        <v>0.2185617295971726</v>
+        <v>0.2189926863572433</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3322976020284401</v>
+        <v>0.323990161977729</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1556862065439291</v>
+        <v>0.1575862065439291</v>
       </c>
       <c r="C42">
-        <v>17.63566228428354</v>
+        <v>13.77913640216812</v>
       </c>
       <c r="D42">
-        <v>73.51566228428358</v>
+        <v>72.26613640216816</v>
       </c>
       <c r="E42">
-        <v>21.88000000000002</v>
+        <v>24.48700000000002</v>
       </c>
       <c r="F42">
-        <v>104.28</v>
+        <v>106.887</v>
       </c>
       <c r="G42">
         <v>48.4</v>
@@ -4725,37 +4725,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M42">
-        <v>24.58922400000001</v>
+        <v>25.20395460000001</v>
       </c>
       <c r="N42">
-        <v>-16.62255733333334</v>
+        <v>-17.23728793333334</v>
       </c>
       <c r="O42">
-        <v>-3.656962613333336</v>
+        <v>-3.792203345333335</v>
       </c>
       <c r="P42">
-        <v>-12.96559472000001</v>
+        <v>-13.44508458800001</v>
       </c>
       <c r="Q42">
-        <v>-6.015594720000007</v>
+        <v>-6.495084588000007</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1134818866683863</v>
+        <v>0.1146290372898844</v>
       </c>
       <c r="T42">
-        <v>1.563092070863426</v>
+        <v>1.589585156810263</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0712778356351004</v>
+        <v>0.06953935183912234</v>
       </c>
       <c r="W42">
-        <v>0.2189926863572433</v>
+        <v>0.219402620836335</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.323990161977729</v>
+        <v>0.3160879629051015</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1575862065439291</v>
+        <v>0.1594862065439291</v>
       </c>
       <c r="C43">
-        <v>13.77913640216812</v>
+        <v>9.964376346324713</v>
       </c>
       <c r="D43">
-        <v>72.26613640216816</v>
+        <v>71.05837634632475</v>
       </c>
       <c r="E43">
-        <v>24.48700000000002</v>
+        <v>27.09400000000002</v>
       </c>
       <c r="F43">
-        <v>106.887</v>
+        <v>109.494</v>
       </c>
       <c r="G43">
         <v>48.4</v>
@@ -4807,37 +4807,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M43">
-        <v>25.20395460000001</v>
+        <v>25.81868520000001</v>
       </c>
       <c r="N43">
-        <v>-17.23728793333334</v>
+        <v>-17.85201853333334</v>
       </c>
       <c r="O43">
-        <v>-3.792203345333335</v>
+        <v>-3.927444077333336</v>
       </c>
       <c r="P43">
-        <v>-13.44508458800001</v>
+        <v>-13.92457445600001</v>
       </c>
       <c r="Q43">
-        <v>-6.495084588000007</v>
+        <v>-6.974574456000007</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1146290372898844</v>
+        <v>0.1158157448293652</v>
       </c>
       <c r="T43">
-        <v>1.589585156810263</v>
+        <v>1.616991797444923</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06953935183912234</v>
+        <v>0.06788365298580991</v>
       </c>
       <c r="W43">
-        <v>0.219402620836335</v>
+        <v>0.219793034625946</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3160879629051015</v>
+        <v>0.3085620590264087</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1594862065439291</v>
+        <v>0.1613862065439291</v>
       </c>
       <c r="C44">
-        <v>9.964376346324727</v>
+        <v>6.189322483369168</v>
       </c>
       <c r="D44">
-        <v>71.05837634632475</v>
+        <v>69.89032248336919</v>
       </c>
       <c r="E44">
-        <v>27.09400000000001</v>
+        <v>29.70100000000001</v>
       </c>
       <c r="F44">
-        <v>109.494</v>
+        <v>112.101</v>
       </c>
       <c r="G44">
         <v>48.4</v>
@@ -4889,37 +4889,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M44">
-        <v>25.8186852</v>
+        <v>26.43341580000001</v>
       </c>
       <c r="N44">
-        <v>-17.85201853333334</v>
+        <v>-18.46674913333334</v>
       </c>
       <c r="O44">
-        <v>-3.927444077333335</v>
+        <v>-4.062684809333335</v>
       </c>
       <c r="P44">
-        <v>-13.92457445600001</v>
+        <v>-14.40406432400001</v>
       </c>
       <c r="Q44">
-        <v>-6.974574456000005</v>
+        <v>-7.454064324000005</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1158157448293652</v>
+        <v>0.1170440912298803</v>
       </c>
       <c r="T44">
-        <v>1.616991797444923</v>
+        <v>1.645360074593079</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06788365298580992</v>
+        <v>0.06630496338148875</v>
       </c>
       <c r="W44">
-        <v>0.219793034625946</v>
+        <v>0.220165289634645</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3085620590264087</v>
+        <v>0.3013861971885852</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1613862065439291</v>
+        <v>0.1632862065439292</v>
       </c>
       <c r="C45">
-        <v>6.189322483369168</v>
+        <v>2.452048414397922</v>
       </c>
       <c r="D45">
-        <v>69.89032248336919</v>
+        <v>68.76004841439794</v>
       </c>
       <c r="E45">
-        <v>29.70100000000001</v>
+        <v>32.30800000000002</v>
       </c>
       <c r="F45">
-        <v>112.101</v>
+        <v>114.708</v>
       </c>
       <c r="G45">
         <v>48.4</v>
@@ -4971,37 +4971,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M45">
-        <v>26.43341580000001</v>
+        <v>27.04814640000001</v>
       </c>
       <c r="N45">
-        <v>-18.46674913333334</v>
+        <v>-19.08147973333334</v>
       </c>
       <c r="O45">
-        <v>-4.062684809333335</v>
+        <v>-4.197925541333335</v>
       </c>
       <c r="P45">
-        <v>-14.40406432400001</v>
+        <v>-14.88355419200001</v>
       </c>
       <c r="Q45">
-        <v>-7.454064324000005</v>
+        <v>-7.933554192000007</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1170440912298803</v>
+        <v>0.1183163071446997</v>
       </c>
       <c r="T45">
-        <v>1.645360074593079</v>
+        <v>1.674741504496527</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06630496338148875</v>
+        <v>0.06479803239554582</v>
       </c>
       <c r="W45">
-        <v>0.220165289634645</v>
+        <v>0.2205206239611303</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3013861971885852</v>
+        <v>0.2945365108888446</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1632862065439292</v>
+        <v>0.1651862065439291</v>
       </c>
       <c r="C46">
-        <v>2.452048414397922</v>
+        <v>-1.249249626969885</v>
       </c>
       <c r="D46">
-        <v>68.76004841439794</v>
+        <v>67.66575037303014</v>
       </c>
       <c r="E46">
-        <v>32.30800000000002</v>
+        <v>34.91500000000002</v>
       </c>
       <c r="F46">
-        <v>114.708</v>
+        <v>117.315</v>
       </c>
       <c r="G46">
         <v>48.4</v>
@@ -5053,37 +5053,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M46">
-        <v>27.04814640000001</v>
+        <v>27.66287700000001</v>
       </c>
       <c r="N46">
-        <v>-19.08147973333334</v>
+        <v>-19.69621033333334</v>
       </c>
       <c r="O46">
-        <v>-4.197925541333335</v>
+        <v>-4.333166273333336</v>
       </c>
       <c r="P46">
-        <v>-14.88355419200001</v>
+        <v>-15.36304406000001</v>
       </c>
       <c r="Q46">
-        <v>-7.933554192000007</v>
+        <v>-8.413044060000008</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1183163071446997</v>
+        <v>0.1196347854564214</v>
       </c>
       <c r="T46">
-        <v>1.674741504496527</v>
+        <v>1.705191350032828</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.06479803239554582</v>
+        <v>0.06335807612008924</v>
       </c>
       <c r="W46">
-        <v>0.2205206239611303</v>
+        <v>0.220860165650883</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2945365108888446</v>
+        <v>0.2879912550913147</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1651862065439291</v>
+        <v>0.1670862065439291</v>
       </c>
       <c r="C47">
-        <v>-1.249249626969885</v>
+        <v>-4.916262380045765</v>
       </c>
       <c r="D47">
-        <v>67.66575037303014</v>
+        <v>66.60573761995427</v>
       </c>
       <c r="E47">
-        <v>34.91500000000002</v>
+        <v>37.52200000000002</v>
       </c>
       <c r="F47">
-        <v>117.315</v>
+        <v>119.922</v>
       </c>
       <c r="G47">
         <v>48.4</v>
@@ -5135,37 +5135,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M47">
-        <v>27.66287700000001</v>
+        <v>28.27760760000001</v>
       </c>
       <c r="N47">
-        <v>-19.69621033333334</v>
+        <v>-20.31094093333334</v>
       </c>
       <c r="O47">
-        <v>-4.333166273333336</v>
+        <v>-4.468407005333336</v>
       </c>
       <c r="P47">
-        <v>-15.36304406000001</v>
+        <v>-15.84253392800001</v>
       </c>
       <c r="Q47">
-        <v>-8.413044060000008</v>
+        <v>-8.892533928000006</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1196347854564214</v>
+        <v>0.121002096298207</v>
       </c>
       <c r="T47">
-        <v>1.705191350032828</v>
+        <v>1.736768967626028</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06335807612008924</v>
+        <v>0.06198072663921774</v>
       </c>
       <c r="W47">
-        <v>0.220860165650883</v>
+        <v>0.2211849446584725</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2879912550913147</v>
+        <v>0.2817305756328079</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1670862065439291</v>
+        <v>0.1689862065439292</v>
       </c>
       <c r="C48">
-        <v>-4.916262380045765</v>
+        <v>-8.550576273608868</v>
       </c>
       <c r="D48">
-        <v>66.60573761995427</v>
+        <v>65.57842372639116</v>
       </c>
       <c r="E48">
-        <v>37.52200000000002</v>
+        <v>40.12900000000002</v>
       </c>
       <c r="F48">
-        <v>119.922</v>
+        <v>122.529</v>
       </c>
       <c r="G48">
         <v>48.4</v>
@@ -5217,37 +5217,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M48">
-        <v>28.27760760000001</v>
+        <v>28.89233820000001</v>
       </c>
       <c r="N48">
-        <v>-20.31094093333334</v>
+        <v>-20.92567153333334</v>
       </c>
       <c r="O48">
-        <v>-4.468407005333336</v>
+        <v>-4.603647737333335</v>
       </c>
       <c r="P48">
-        <v>-15.84253392800001</v>
+        <v>-16.32202379600001</v>
       </c>
       <c r="Q48">
-        <v>-8.892533928000006</v>
+        <v>-9.372023796000008</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.121002096298207</v>
+        <v>0.1224210037755317</v>
       </c>
       <c r="T48">
-        <v>1.736768967626028</v>
+        <v>1.769538193430293</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06198072663921774</v>
+        <v>0.06066198777455353</v>
       </c>
       <c r="W48">
-        <v>0.2211849446584725</v>
+        <v>0.2214959032827603</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2817305756328079</v>
+        <v>0.2757363080661523</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1689862065439292</v>
+        <v>0.1708862065439291</v>
       </c>
       <c r="C49">
-        <v>-8.550576273608868</v>
+        <v>-12.15368134804315</v>
       </c>
       <c r="D49">
-        <v>65.57842372639116</v>
+        <v>64.5823186519569</v>
       </c>
       <c r="E49">
-        <v>40.12900000000002</v>
+        <v>42.73600000000003</v>
       </c>
       <c r="F49">
-        <v>122.529</v>
+        <v>125.136</v>
       </c>
       <c r="G49">
         <v>48.4</v>
@@ -5299,37 +5299,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M49">
-        <v>28.89233820000001</v>
+        <v>29.50706880000001</v>
       </c>
       <c r="N49">
-        <v>-20.92567153333334</v>
+        <v>-21.54040213333334</v>
       </c>
       <c r="O49">
-        <v>-4.603647737333335</v>
+        <v>-4.738888469333336</v>
       </c>
       <c r="P49">
-        <v>-16.32202379600001</v>
+        <v>-16.80151366400001</v>
       </c>
       <c r="Q49">
-        <v>-9.372023796000008</v>
+        <v>-9.851513664000009</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1224210037755317</v>
+        <v>0.1238944846173688</v>
       </c>
       <c r="T49">
-        <v>1.769538193430293</v>
+        <v>1.803567774073183</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06066198777455353</v>
+        <v>0.05939819636258366</v>
       </c>
       <c r="W49">
-        <v>0.2214959032827603</v>
+        <v>0.2217939052977028</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2757363080661523</v>
+        <v>0.2699918016481075</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1708862065439291</v>
+        <v>0.1727862065439291</v>
       </c>
       <c r="C50">
-        <v>-12.15368134804314</v>
+        <v>-15.72697846627597</v>
       </c>
       <c r="D50">
-        <v>64.5823186519569</v>
+        <v>63.61602153372405</v>
       </c>
       <c r="E50">
-        <v>42.73600000000002</v>
+        <v>45.34300000000002</v>
       </c>
       <c r="F50">
-        <v>125.136</v>
+        <v>127.743</v>
       </c>
       <c r="G50">
         <v>48.4</v>
@@ -5381,37 +5381,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M50">
-        <v>29.50706880000001</v>
+        <v>30.12179940000001</v>
       </c>
       <c r="N50">
-        <v>-21.54040213333334</v>
+        <v>-22.15513273333334</v>
       </c>
       <c r="O50">
-        <v>-4.738888469333335</v>
+        <v>-4.874129201333336</v>
       </c>
       <c r="P50">
-        <v>-16.80151366400001</v>
+        <v>-17.28100353200001</v>
       </c>
       <c r="Q50">
-        <v>-9.851513664000006</v>
+        <v>-10.33100353200001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1238944846173688</v>
+        <v>0.125425749021631</v>
       </c>
       <c r="T50">
-        <v>1.803567774073183</v>
+        <v>1.838931848074618</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05939819636258367</v>
+        <v>0.05818598827355135</v>
       </c>
       <c r="W50">
-        <v>0.2217939052977028</v>
+        <v>0.2220797439650966</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2699918016481075</v>
+        <v>0.2644817648797788</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1727862065439291</v>
+        <v>0.1746862065439291</v>
       </c>
       <c r="C51">
-        <v>-15.72697846627597</v>
+        <v>-19.27178588690853</v>
       </c>
       <c r="D51">
-        <v>63.61602153372405</v>
+        <v>62.67821411309149</v>
       </c>
       <c r="E51">
-        <v>45.34300000000002</v>
+        <v>47.95000000000002</v>
       </c>
       <c r="F51">
-        <v>127.743</v>
+        <v>130.35</v>
       </c>
       <c r="G51">
         <v>48.4</v>
@@ -5463,37 +5463,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M51">
-        <v>30.12179940000001</v>
+        <v>30.73653000000001</v>
       </c>
       <c r="N51">
-        <v>-22.15513273333334</v>
+        <v>-22.76986333333334</v>
       </c>
       <c r="O51">
-        <v>-4.874129201333336</v>
+        <v>-5.009369933333335</v>
       </c>
       <c r="P51">
-        <v>-17.28100353200001</v>
+        <v>-17.7604934</v>
       </c>
       <c r="Q51">
-        <v>-10.33100353200001</v>
+        <v>-10.81049340000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.125425749021631</v>
+        <v>0.1270182640020636</v>
       </c>
       <c r="T51">
-        <v>1.838931848074618</v>
+        <v>1.875710485036111</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05818598827355135</v>
+        <v>0.05702226850808032</v>
       </c>
       <c r="W51">
-        <v>0.2220797439650966</v>
+        <v>0.2223541490857947</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2644817648797788</v>
+        <v>0.2591921295821833</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1746862065439291</v>
+        <v>0.1765862065439291</v>
       </c>
       <c r="C52">
-        <v>-19.27178588690853</v>
+        <v>-22.78934526439818</v>
       </c>
       <c r="D52">
-        <v>62.67821411309149</v>
+        <v>61.76765473560185</v>
       </c>
       <c r="E52">
-        <v>47.95000000000002</v>
+        <v>50.55700000000002</v>
       </c>
       <c r="F52">
-        <v>130.35</v>
+        <v>132.957</v>
       </c>
       <c r="G52">
         <v>48.4</v>
@@ -5545,37 +5545,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M52">
-        <v>30.73653000000001</v>
+        <v>31.35126060000001</v>
       </c>
       <c r="N52">
-        <v>-22.76986333333334</v>
+        <v>-23.38459393333334</v>
       </c>
       <c r="O52">
-        <v>-5.009369933333335</v>
+        <v>-5.144610665333335</v>
       </c>
       <c r="P52">
-        <v>-17.7604934</v>
+        <v>-18.23998326800001</v>
       </c>
       <c r="Q52">
-        <v>-10.81049340000001</v>
+        <v>-11.28998326800001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1270182640020636</v>
+        <v>0.1286757795939424</v>
       </c>
       <c r="T52">
-        <v>1.875710485036111</v>
+        <v>1.913990290853174</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05702226850808032</v>
+        <v>0.05590418481184345</v>
       </c>
       <c r="W52">
-        <v>0.2223541490857947</v>
+        <v>0.2226177932213673</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2591921295821833</v>
+        <v>0.2541099309629248</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1765862065439291</v>
+        <v>0.1784862065439291</v>
       </c>
       <c r="C53">
-        <v>-22.78934526439818</v>
+        <v>-26.28082713372336</v>
       </c>
       <c r="D53">
-        <v>61.76765473560185</v>
+        <v>60.88317286627665</v>
       </c>
       <c r="E53">
-        <v>50.55700000000002</v>
+        <v>53.16400000000002</v>
       </c>
       <c r="F53">
-        <v>132.957</v>
+        <v>135.564</v>
       </c>
       <c r="G53">
         <v>48.4</v>
@@ -5627,37 +5627,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M53">
-        <v>31.35126060000001</v>
+        <v>31.9659912</v>
       </c>
       <c r="N53">
-        <v>-23.38459393333334</v>
+        <v>-23.99932453333334</v>
       </c>
       <c r="O53">
-        <v>-5.144610665333335</v>
+        <v>-5.279851397333335</v>
       </c>
       <c r="P53">
-        <v>-18.23998326800001</v>
+        <v>-18.719473136</v>
       </c>
       <c r="Q53">
-        <v>-11.28998326800001</v>
+        <v>-11.76947313600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1286757795939424</v>
+        <v>0.1304023583354829</v>
       </c>
       <c r="T53">
-        <v>1.913990290853174</v>
+        <v>1.953865088579282</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05590418481184345</v>
+        <v>0.05482910433469262</v>
       </c>
       <c r="W53">
-        <v>0.2226177932213673</v>
+        <v>0.2228712971978795</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2541099309629248</v>
+        <v>0.24922320152133</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1784862065439291</v>
+        <v>0.1803862065439291</v>
       </c>
       <c r="C54">
-        <v>-26.28082713372336</v>
+        <v>-29.7473359304749</v>
       </c>
       <c r="D54">
-        <v>60.88317286627665</v>
+        <v>60.02366406952512</v>
       </c>
       <c r="E54">
-        <v>53.16400000000002</v>
+        <v>55.77100000000002</v>
       </c>
       <c r="F54">
-        <v>135.564</v>
+        <v>138.171</v>
       </c>
       <c r="G54">
         <v>48.4</v>
@@ -5709,37 +5709,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M54">
-        <v>31.9659912</v>
+        <v>32.58072180000001</v>
       </c>
       <c r="N54">
-        <v>-23.99932453333334</v>
+        <v>-24.61405513333334</v>
       </c>
       <c r="O54">
-        <v>-5.279851397333335</v>
+        <v>-5.415092129333335</v>
       </c>
       <c r="P54">
-        <v>-18.719473136</v>
+        <v>-19.19896300400001</v>
       </c>
       <c r="Q54">
-        <v>-11.76947313600001</v>
+        <v>-12.24896300400001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1304023583354829</v>
+        <v>0.1322024085128336</v>
       </c>
       <c r="T54">
-        <v>1.953865088579282</v>
+        <v>1.995436686208629</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05482910433469262</v>
+        <v>0.05379459293215125</v>
       </c>
       <c r="W54">
-        <v>0.2228712971978795</v>
+        <v>0.2231152349865987</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.24922320152133</v>
+        <v>0.2445208769643238</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1803862065439291</v>
+        <v>0.1822862065439291</v>
       </c>
       <c r="C55">
-        <v>-29.7473359304749</v>
+        <v>-33.18991459164454</v>
       </c>
       <c r="D55">
-        <v>60.02366406952512</v>
+        <v>59.18808540835549</v>
       </c>
       <c r="E55">
-        <v>55.77100000000002</v>
+        <v>58.37800000000001</v>
       </c>
       <c r="F55">
-        <v>138.171</v>
+        <v>140.778</v>
       </c>
       <c r="G55">
         <v>48.4</v>
@@ -5791,37 +5791,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M55">
-        <v>32.58072180000001</v>
+        <v>33.19545240000001</v>
       </c>
       <c r="N55">
-        <v>-24.61405513333334</v>
+        <v>-25.22878573333334</v>
       </c>
       <c r="O55">
-        <v>-5.415092129333335</v>
+        <v>-5.550332861333335</v>
       </c>
       <c r="P55">
-        <v>-19.19896300400001</v>
+        <v>-19.67845287200001</v>
       </c>
       <c r="Q55">
-        <v>-12.24896300400001</v>
+        <v>-12.72845287200001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1322024085128336</v>
+        <v>0.1340807217413735</v>
       </c>
       <c r="T55">
-        <v>1.995436686208629</v>
+        <v>2.038815744604468</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05379459293215125</v>
+        <v>0.05279839676674104</v>
       </c>
       <c r="W55">
-        <v>0.2231152349865987</v>
+        <v>0.2233501380424025</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2445208769643238</v>
+        <v>0.2399927125760956</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1822862065439291</v>
+        <v>0.1841862065439291</v>
       </c>
       <c r="C56">
-        <v>-33.18991459164454</v>
+        <v>-36.60954877740915</v>
       </c>
       <c r="D56">
-        <v>59.18808540835549</v>
+        <v>58.3754512225909</v>
       </c>
       <c r="E56">
-        <v>58.37800000000001</v>
+        <v>60.98500000000004</v>
       </c>
       <c r="F56">
-        <v>140.778</v>
+        <v>143.385</v>
       </c>
       <c r="G56">
         <v>48.4</v>
@@ -5873,37 +5873,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M56">
-        <v>33.19545240000001</v>
+        <v>33.81018300000001</v>
       </c>
       <c r="N56">
-        <v>-25.22878573333334</v>
+        <v>-25.84351633333334</v>
       </c>
       <c r="O56">
-        <v>-5.550332861333335</v>
+        <v>-5.685573593333336</v>
       </c>
       <c r="P56">
-        <v>-19.67845287200001</v>
+        <v>-20.15794274000001</v>
       </c>
       <c r="Q56">
-        <v>-12.72845287200001</v>
+        <v>-13.20794274000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1340807217413735</v>
+        <v>0.1360425155578484</v>
       </c>
       <c r="T56">
-        <v>2.038815744604468</v>
+        <v>2.084122761151234</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05279839676674104</v>
+        <v>0.05183842591643666</v>
       </c>
       <c r="W56">
-        <v>0.2233501380424025</v>
+        <v>0.2235764991689043</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2399927125760956</v>
+        <v>0.2356292087110757</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1841862065439291</v>
+        <v>0.1860862065439291</v>
       </c>
       <c r="C57">
-        <v>-36.60954877740915</v>
+        <v>-40.00717074984229</v>
       </c>
       <c r="D57">
-        <v>58.3754512225909</v>
+        <v>57.58482925015777</v>
       </c>
       <c r="E57">
-        <v>60.98500000000004</v>
+        <v>63.59200000000004</v>
       </c>
       <c r="F57">
-        <v>143.385</v>
+        <v>145.992</v>
       </c>
       <c r="G57">
         <v>48.4</v>
@@ -5955,37 +5955,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M57">
-        <v>33.81018300000001</v>
+        <v>34.42491360000001</v>
       </c>
       <c r="N57">
-        <v>-25.84351633333334</v>
+        <v>-26.45824693333335</v>
       </c>
       <c r="O57">
-        <v>-5.685573593333336</v>
+        <v>-5.820814325333336</v>
       </c>
       <c r="P57">
-        <v>-20.15794274000001</v>
+        <v>-20.63743260800001</v>
       </c>
       <c r="Q57">
-        <v>-13.20794274000001</v>
+        <v>-13.68743260800001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1360425155578484</v>
+        <v>0.1380934818205268</v>
       </c>
       <c r="T57">
-        <v>2.084122761151234</v>
+        <v>2.131489187541035</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05183842591643666</v>
+        <v>0.05091273973935743</v>
       </c>
       <c r="W57">
-        <v>0.2235764991689043</v>
+        <v>0.2237947759694595</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2356292087110757</v>
+        <v>0.2314215442698064</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1860862065439291</v>
+        <v>0.1879862065439291</v>
       </c>
       <c r="C58">
-        <v>-40.00717074984229</v>
+        <v>-43.38366294064417</v>
       </c>
       <c r="D58">
-        <v>57.58482925015777</v>
+        <v>56.81533705935588</v>
       </c>
       <c r="E58">
-        <v>63.59200000000004</v>
+        <v>66.19900000000004</v>
       </c>
       <c r="F58">
-        <v>145.992</v>
+        <v>148.599</v>
       </c>
       <c r="G58">
         <v>48.4</v>
@@ -6037,37 +6037,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M58">
-        <v>34.42491360000001</v>
+        <v>35.03964420000001</v>
       </c>
       <c r="N58">
-        <v>-26.45824693333335</v>
+        <v>-27.07297753333335</v>
       </c>
       <c r="O58">
-        <v>-5.820814325333336</v>
+        <v>-5.956055057333336</v>
       </c>
       <c r="P58">
-        <v>-20.63743260800001</v>
+        <v>-21.11692247600001</v>
       </c>
       <c r="Q58">
-        <v>-13.68743260800001</v>
+        <v>-14.16692247600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1380934818205268</v>
+        <v>0.1402398418628646</v>
       </c>
       <c r="T58">
-        <v>2.131489187541035</v>
+        <v>2.181058703530362</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05091273973935743</v>
+        <v>0.05001953377901782</v>
       </c>
       <c r="W58">
-        <v>0.2237947759694595</v>
+        <v>0.2240053939349076</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2314215442698064</v>
+        <v>0.2273615171773538</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1879862065439291</v>
+        <v>0.1898862065439291</v>
       </c>
       <c r="C59">
-        <v>-43.38366294064417</v>
+        <v>-46.73986123659532</v>
       </c>
       <c r="D59">
-        <v>56.81533705935588</v>
+        <v>56.06613876340474</v>
       </c>
       <c r="E59">
-        <v>66.19900000000004</v>
+        <v>68.80600000000004</v>
       </c>
       <c r="F59">
-        <v>148.599</v>
+        <v>151.206</v>
       </c>
       <c r="G59">
         <v>48.4</v>
@@ -6119,37 +6119,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M59">
-        <v>35.03964420000001</v>
+        <v>35.65437480000001</v>
       </c>
       <c r="N59">
-        <v>-27.07297753333335</v>
+        <v>-27.68770813333335</v>
       </c>
       <c r="O59">
-        <v>-5.956055057333336</v>
+        <v>-6.091295789333337</v>
       </c>
       <c r="P59">
-        <v>-21.11692247600001</v>
+        <v>-21.59641234400001</v>
       </c>
       <c r="Q59">
-        <v>-14.16692247600001</v>
+        <v>-14.64641234400001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1402398418628646</v>
+        <v>0.1424884095262662</v>
       </c>
       <c r="T59">
-        <v>2.181058703530362</v>
+        <v>2.232988672662037</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05001953377901782</v>
+        <v>0.04915712802420717</v>
       </c>
       <c r="W59">
-        <v>0.2240053939349076</v>
+        <v>0.224208749211892</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2273615171773538</v>
+        <v>0.2234414910191235</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1898862065439291</v>
+        <v>0.1917862065439291</v>
       </c>
       <c r="C60">
-        <v>-46.73986123659529</v>
+        <v>-50.07655800845032</v>
       </c>
       <c r="D60">
-        <v>56.06613876340474</v>
+        <v>55.3364419915497</v>
       </c>
       <c r="E60">
-        <v>68.80600000000001</v>
+        <v>71.41300000000001</v>
       </c>
       <c r="F60">
-        <v>151.206</v>
+        <v>153.813</v>
       </c>
       <c r="G60">
         <v>48.4</v>
@@ -6201,37 +6201,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M60">
-        <v>35.65437480000001</v>
+        <v>36.26910540000001</v>
       </c>
       <c r="N60">
-        <v>-27.68770813333334</v>
+        <v>-28.30243873333334</v>
       </c>
       <c r="O60">
-        <v>-6.091295789333335</v>
+        <v>-6.226536521333336</v>
       </c>
       <c r="P60">
-        <v>-21.59641234400001</v>
+        <v>-22.07590221200001</v>
       </c>
       <c r="Q60">
-        <v>-14.64641234400001</v>
+        <v>-15.12590221200001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1424884095262662</v>
+        <v>0.1448466634171507</v>
       </c>
       <c r="T60">
-        <v>2.232988672662036</v>
+        <v>2.287451811019647</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04915712802420718</v>
+        <v>0.04832395636277994</v>
       </c>
       <c r="W60">
-        <v>0.224208749211892</v>
+        <v>0.2244052110896565</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2234414910191235</v>
+        <v>0.2196543471035451</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1917862065439291</v>
+        <v>0.1936862065439291</v>
       </c>
       <c r="C61">
-        <v>-50.07655800845032</v>
+        <v>-53.39450490634584</v>
       </c>
       <c r="D61">
-        <v>55.3364419915497</v>
+        <v>54.62549509365417</v>
       </c>
       <c r="E61">
-        <v>71.41300000000001</v>
+        <v>74.02000000000001</v>
       </c>
       <c r="F61">
-        <v>153.813</v>
+        <v>156.42</v>
       </c>
       <c r="G61">
         <v>48.4</v>
@@ -6283,37 +6283,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M61">
-        <v>36.26910540000001</v>
+        <v>36.883836</v>
       </c>
       <c r="N61">
-        <v>-28.30243873333334</v>
+        <v>-28.91716933333334</v>
       </c>
       <c r="O61">
-        <v>-6.226536521333336</v>
+        <v>-6.361777253333334</v>
       </c>
       <c r="P61">
-        <v>-22.07590221200001</v>
+        <v>-22.55539208</v>
       </c>
       <c r="Q61">
-        <v>-15.12590221200001</v>
+        <v>-15.60539208</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1448466634171507</v>
+        <v>0.1473228300025795</v>
       </c>
       <c r="T61">
-        <v>2.287451811019647</v>
+        <v>2.344638106295138</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04832395636277994</v>
+        <v>0.04751855709006694</v>
       </c>
       <c r="W61">
-        <v>0.2244052110896565</v>
+        <v>0.2245951242381622</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2196543471035451</v>
+        <v>0.2159934413184861</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1936862065439291</v>
+        <v>0.1955862065439291</v>
       </c>
       <c r="C62">
-        <v>-53.39450490634584</v>
+        <v>-56.69441544245389</v>
       </c>
       <c r="D62">
-        <v>54.62549509365417</v>
+        <v>53.93258455754613</v>
       </c>
       <c r="E62">
-        <v>74.02000000000001</v>
+        <v>76.62700000000001</v>
       </c>
       <c r="F62">
-        <v>156.42</v>
+        <v>159.027</v>
       </c>
       <c r="G62">
         <v>48.4</v>
@@ -6365,37 +6365,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M62">
-        <v>36.883836</v>
+        <v>37.4985666</v>
       </c>
       <c r="N62">
-        <v>-28.91716933333334</v>
+        <v>-29.53189993333334</v>
       </c>
       <c r="O62">
-        <v>-6.361777253333334</v>
+        <v>-6.497017985333335</v>
       </c>
       <c r="P62">
-        <v>-22.55539208</v>
+        <v>-23.03488194800001</v>
       </c>
       <c r="Q62">
-        <v>-15.60539208</v>
+        <v>-16.08488194800001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1473228300025795</v>
+        <v>0.1499259794898251</v>
       </c>
       <c r="T62">
-        <v>2.344638106295138</v>
+        <v>2.404757032097578</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04751855709006694</v>
+        <v>0.04673956435088551</v>
       </c>
       <c r="W62">
-        <v>0.2245951242381622</v>
+        <v>0.2247788107260612</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2159934413184861</v>
+        <v>0.2124525652312977</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1955862065439291</v>
+        <v>0.1974862065439291</v>
       </c>
       <c r="C63">
-        <v>-56.69441544245389</v>
+        <v>-59.97696737953568</v>
       </c>
       <c r="D63">
-        <v>53.93258455754613</v>
+        <v>53.25703262046434</v>
       </c>
       <c r="E63">
-        <v>76.62700000000001</v>
+        <v>79.23400000000001</v>
       </c>
       <c r="F63">
-        <v>159.027</v>
+        <v>161.634</v>
       </c>
       <c r="G63">
         <v>48.4</v>
@@ -6447,37 +6447,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M63">
-        <v>37.4985666</v>
+        <v>38.11329720000001</v>
       </c>
       <c r="N63">
-        <v>-29.53189993333334</v>
+        <v>-30.14663053333334</v>
       </c>
       <c r="O63">
-        <v>-6.497017985333335</v>
+        <v>-6.632258717333335</v>
       </c>
       <c r="P63">
-        <v>-23.03488194800001</v>
+        <v>-23.514371816</v>
       </c>
       <c r="Q63">
-        <v>-16.08488194800001</v>
+        <v>-16.564371816</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1499259794898251</v>
+        <v>0.1526661368448205</v>
       </c>
       <c r="T63">
-        <v>2.404757032097578</v>
+        <v>2.468040111889619</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04673956435088551</v>
+        <v>0.0459857004097422</v>
       </c>
       <c r="W63">
-        <v>0.2247788107260612</v>
+        <v>0.2249565718433828</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2124525652312977</v>
+        <v>0.2090259109533736</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1974862065439291</v>
+        <v>0.1993862065439291</v>
       </c>
       <c r="C64">
-        <v>-59.97696737953568</v>
+        <v>-63.24280494220407</v>
       </c>
       <c r="D64">
-        <v>53.25703262046434</v>
+        <v>52.59819505779597</v>
       </c>
       <c r="E64">
-        <v>79.23400000000001</v>
+        <v>81.84100000000004</v>
       </c>
       <c r="F64">
-        <v>161.634</v>
+        <v>164.241</v>
       </c>
       <c r="G64">
         <v>48.4</v>
@@ -6529,37 +6529,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M64">
-        <v>38.11329720000001</v>
+        <v>38.72802780000001</v>
       </c>
       <c r="N64">
-        <v>-30.14663053333334</v>
+        <v>-30.76136113333335</v>
       </c>
       <c r="O64">
-        <v>-6.632258717333335</v>
+        <v>-6.767499449333337</v>
       </c>
       <c r="P64">
-        <v>-23.514371816</v>
+        <v>-23.99386168400001</v>
       </c>
       <c r="Q64">
-        <v>-16.564371816</v>
+        <v>-17.04386168400001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1526661368448205</v>
+        <v>0.1555544108135994</v>
       </c>
       <c r="T64">
-        <v>2.468040111889619</v>
+        <v>2.534743898697447</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0459857004097422</v>
+        <v>0.0452557686572066</v>
       </c>
       <c r="W64">
-        <v>0.2249565718433828</v>
+        <v>0.2251286897506307</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2090259109533736</v>
+        <v>0.2057080393509391</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1993862065439291</v>
+        <v>0.2012862065439291</v>
       </c>
       <c r="C65">
-        <v>-63.24280494220407</v>
+        <v>-66.49254086605966</v>
       </c>
       <c r="D65">
-        <v>52.59819505779597</v>
+        <v>51.95545913394039</v>
       </c>
       <c r="E65">
-        <v>81.84100000000004</v>
+        <v>84.44800000000004</v>
       </c>
       <c r="F65">
-        <v>164.241</v>
+        <v>166.848</v>
       </c>
       <c r="G65">
         <v>48.4</v>
@@ -6611,37 +6611,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M65">
-        <v>38.72802780000001</v>
+        <v>39.34275840000001</v>
       </c>
       <c r="N65">
-        <v>-30.76136113333335</v>
+        <v>-31.37609173333334</v>
       </c>
       <c r="O65">
-        <v>-6.767499449333337</v>
+        <v>-6.902740181333336</v>
       </c>
       <c r="P65">
-        <v>-23.99386168400001</v>
+        <v>-24.47335155200001</v>
       </c>
       <c r="Q65">
-        <v>-17.04386168400001</v>
+        <v>-17.52335155200001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1555544108135994</v>
+        <v>0.1586031444473106</v>
       </c>
       <c r="T65">
-        <v>2.534743898697447</v>
+        <v>2.605153451439043</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0452557686572066</v>
+        <v>0.04454864727193775</v>
       </c>
       <c r="W65">
-        <v>0.2251286897506307</v>
+        <v>0.2252954289732771</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2057080393509391</v>
+        <v>0.2024938512360807</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2012862065439291</v>
+        <v>0.2031862065439291</v>
       </c>
       <c r="C66">
-        <v>-66.49254086605966</v>
+        <v>-69.72675829840136</v>
       </c>
       <c r="D66">
-        <v>51.95545913394039</v>
+        <v>51.32824170159867</v>
       </c>
       <c r="E66">
-        <v>84.44800000000004</v>
+        <v>87.05500000000004</v>
       </c>
       <c r="F66">
-        <v>166.848</v>
+        <v>169.455</v>
       </c>
       <c r="G66">
         <v>48.4</v>
@@ -6693,37 +6693,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M66">
-        <v>39.34275840000001</v>
+        <v>39.95748900000001</v>
       </c>
       <c r="N66">
-        <v>-31.37609173333334</v>
+        <v>-31.99082233333334</v>
       </c>
       <c r="O66">
-        <v>-6.902740181333336</v>
+        <v>-7.037980913333336</v>
       </c>
       <c r="P66">
-        <v>-24.47335155200001</v>
+        <v>-24.95284142000001</v>
       </c>
       <c r="Q66">
-        <v>-17.52335155200001</v>
+        <v>-18.00284142000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1586031444473106</v>
+        <v>0.1618260914315194</v>
       </c>
       <c r="T66">
-        <v>2.605153451439043</v>
+        <v>2.679586407194444</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04454864727193775</v>
+        <v>0.0438632834677541</v>
       </c>
       <c r="W66">
-        <v>0.2252954289732771</v>
+        <v>0.2254570377583036</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2024938512360807</v>
+        <v>0.199378561217064</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2031862065439291</v>
+        <v>0.2050862065439291</v>
       </c>
       <c r="C67">
-        <v>-69.72675829840136</v>
+        <v>-72.94601256290443</v>
       </c>
       <c r="D67">
-        <v>51.32824170159867</v>
+        <v>50.71598743709561</v>
       </c>
       <c r="E67">
-        <v>87.05500000000004</v>
+        <v>89.66200000000003</v>
       </c>
       <c r="F67">
-        <v>169.455</v>
+        <v>172.062</v>
       </c>
       <c r="G67">
         <v>48.4</v>
@@ -6775,37 +6775,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M67">
-        <v>39.95748900000001</v>
+        <v>40.57221960000001</v>
       </c>
       <c r="N67">
-        <v>-31.99082233333334</v>
+        <v>-32.60555293333334</v>
       </c>
       <c r="O67">
-        <v>-7.037980913333336</v>
+        <v>-7.173221645333335</v>
       </c>
       <c r="P67">
-        <v>-24.95284142000001</v>
+        <v>-25.43233128800001</v>
       </c>
       <c r="Q67">
-        <v>-18.00284142000001</v>
+        <v>-18.48233128800001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1618260914315194</v>
+        <v>0.1652386235324465</v>
       </c>
       <c r="T67">
-        <v>2.679586407194444</v>
+        <v>2.758397772111928</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0438632834677541</v>
+        <v>0.04319868826369722</v>
       </c>
       <c r="W67">
-        <v>0.2254570377583036</v>
+        <v>0.2256137493074202</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.199378561217064</v>
+        <v>0.1963576739258965</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2050862065439291</v>
+        <v>0.2069862065439291</v>
       </c>
       <c r="C68">
-        <v>-72.94601256290443</v>
+        <v>-76.15083279949037</v>
       </c>
       <c r="D68">
-        <v>50.71598743709561</v>
+        <v>50.11816720050967</v>
       </c>
       <c r="E68">
-        <v>89.66200000000003</v>
+        <v>92.26900000000003</v>
       </c>
       <c r="F68">
-        <v>172.062</v>
+        <v>174.669</v>
       </c>
       <c r="G68">
         <v>48.4</v>
@@ -6857,37 +6857,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M68">
-        <v>40.57221960000001</v>
+        <v>41.18695020000001</v>
       </c>
       <c r="N68">
-        <v>-32.60555293333334</v>
+        <v>-33.22028353333334</v>
       </c>
       <c r="O68">
-        <v>-7.173221645333335</v>
+        <v>-7.308462377333336</v>
       </c>
       <c r="P68">
-        <v>-25.43233128800001</v>
+        <v>-25.91182115600001</v>
       </c>
       <c r="Q68">
-        <v>-18.48233128800001</v>
+        <v>-18.96182115600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1652386235324465</v>
+        <v>0.1688579757607024</v>
       </c>
       <c r="T68">
-        <v>2.758397772111928</v>
+        <v>2.841985583388047</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04319868826369722</v>
+        <v>0.042553931722448</v>
       </c>
       <c r="W68">
-        <v>0.2256137493074202</v>
+        <v>0.2257657828998468</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1963576739258965</v>
+        <v>0.1934269623747636</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2069862065439291</v>
+        <v>0.2088862065439291</v>
       </c>
       <c r="C69">
-        <v>-76.15083279949037</v>
+        <v>-79.34172348956734</v>
       </c>
       <c r="D69">
-        <v>50.11816720050967</v>
+        <v>49.5342765104327</v>
       </c>
       <c r="E69">
-        <v>92.26900000000003</v>
+        <v>94.87600000000003</v>
       </c>
       <c r="F69">
-        <v>174.669</v>
+        <v>177.276</v>
       </c>
       <c r="G69">
         <v>48.4</v>
@@ -6939,37 +6939,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M69">
-        <v>41.18695020000001</v>
+        <v>41.80168080000001</v>
       </c>
       <c r="N69">
-        <v>-33.22028353333334</v>
+        <v>-33.83501413333335</v>
       </c>
       <c r="O69">
-        <v>-7.308462377333336</v>
+        <v>-7.443703109333336</v>
       </c>
       <c r="P69">
-        <v>-25.91182115600001</v>
+        <v>-26.39131102400001</v>
       </c>
       <c r="Q69">
-        <v>-18.96182115600001</v>
+        <v>-19.44131102400001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1688579757607024</v>
+        <v>0.1727035375032244</v>
       </c>
       <c r="T69">
-        <v>2.841985583388047</v>
+        <v>2.930797632868924</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.042553931722448</v>
+        <v>0.04192813860888259</v>
       </c>
       <c r="W69">
-        <v>0.2257657828998468</v>
+        <v>0.2259133449160255</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1934269623747636</v>
+        <v>0.1905824482221936</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2088862065439291</v>
+        <v>0.2107862065439291</v>
       </c>
       <c r="C70">
-        <v>-79.34172348956734</v>
+        <v>-82.51916587588138</v>
       </c>
       <c r="D70">
-        <v>49.5342765104327</v>
+        <v>48.96383412411866</v>
       </c>
       <c r="E70">
-        <v>94.87600000000003</v>
+        <v>97.48300000000003</v>
       </c>
       <c r="F70">
-        <v>177.276</v>
+        <v>179.883</v>
       </c>
       <c r="G70">
         <v>48.4</v>
@@ -7021,37 +7021,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M70">
-        <v>41.80168080000001</v>
+        <v>42.41641140000001</v>
       </c>
       <c r="N70">
-        <v>-33.83501413333335</v>
+        <v>-34.44974473333334</v>
       </c>
       <c r="O70">
-        <v>-7.443703109333336</v>
+        <v>-7.578943841333335</v>
       </c>
       <c r="P70">
-        <v>-26.39131102400001</v>
+        <v>-26.87080089200001</v>
       </c>
       <c r="Q70">
-        <v>-19.44131102400001</v>
+        <v>-19.92080089200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1727035375032244</v>
+        <v>0.1767972000033284</v>
       </c>
       <c r="T70">
-        <v>2.930797632868924</v>
+        <v>3.025339491993727</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04192813860888259</v>
+        <v>0.04132048442614517</v>
       </c>
       <c r="W70">
-        <v>0.2259133449160255</v>
+        <v>0.226056629772315</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1905824482221936</v>
+        <v>0.1878203837552054</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2107862065439291</v>
+        <v>0.2126862065439292</v>
       </c>
       <c r="C71">
-        <v>-82.51916587588138</v>
+        <v>-85.68361928537774</v>
       </c>
       <c r="D71">
-        <v>48.96383412411866</v>
+        <v>48.4063807146223</v>
       </c>
       <c r="E71">
-        <v>97.48300000000003</v>
+        <v>100.09</v>
       </c>
       <c r="F71">
-        <v>179.883</v>
+        <v>182.49</v>
       </c>
       <c r="G71">
         <v>48.4</v>
@@ -7103,37 +7103,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M71">
-        <v>42.41641140000001</v>
+        <v>43.03114200000001</v>
       </c>
       <c r="N71">
-        <v>-34.44974473333334</v>
+        <v>-35.06447533333334</v>
       </c>
       <c r="O71">
-        <v>-7.578943841333335</v>
+        <v>-7.714184573333335</v>
       </c>
       <c r="P71">
-        <v>-26.87080089200001</v>
+        <v>-27.35029076000001</v>
       </c>
       <c r="Q71">
-        <v>-19.92080089200001</v>
+        <v>-20.40029076000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1767972000033284</v>
+        <v>0.1811637733367727</v>
       </c>
       <c r="T71">
-        <v>3.025339491993727</v>
+        <v>3.126184141726852</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04132048442614517</v>
+        <v>0.04073019179148595</v>
       </c>
       <c r="W71">
-        <v>0.226056629772315</v>
+        <v>0.2261958207755676</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1878203837552054</v>
+        <v>0.1851372354158453</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2126862065439292</v>
+        <v>0.2145862065439292</v>
       </c>
       <c r="C72">
-        <v>-85.68361928537774</v>
+        <v>-88.8355223627145</v>
       </c>
       <c r="D72">
-        <v>48.4063807146223</v>
+        <v>47.86147763728556</v>
       </c>
       <c r="E72">
-        <v>100.09</v>
+        <v>102.6970000000001</v>
       </c>
       <c r="F72">
-        <v>182.49</v>
+        <v>185.0970000000001</v>
       </c>
       <c r="G72">
         <v>48.4</v>
@@ -7185,37 +7185,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M72">
-        <v>43.03114200000001</v>
+        <v>43.64587260000002</v>
       </c>
       <c r="N72">
-        <v>-35.06447533333334</v>
+        <v>-35.67920593333335</v>
       </c>
       <c r="O72">
-        <v>-7.714184573333335</v>
+        <v>-7.849425305333337</v>
       </c>
       <c r="P72">
-        <v>-27.35029076000001</v>
+        <v>-27.82978062800001</v>
       </c>
       <c r="Q72">
-        <v>-20.40029076000001</v>
+        <v>-20.87978062800001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1811637733367727</v>
+        <v>0.1858314896587304</v>
       </c>
       <c r="T72">
-        <v>3.126184141726852</v>
+        <v>3.233983594889847</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04073019179148595</v>
+        <v>0.04015652711836642</v>
       </c>
       <c r="W72">
-        <v>0.2261958207755676</v>
+        <v>0.2263310909054892</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1851372354158453</v>
+        <v>0.1825296687198474</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2145862065439291</v>
+        <v>0.2164862065439291</v>
       </c>
       <c r="C73">
-        <v>-88.83552236271447</v>
+        <v>-91.97529422139094</v>
       </c>
       <c r="D73">
-        <v>47.86147763728556</v>
+        <v>47.3287057786091</v>
       </c>
       <c r="E73">
-        <v>102.697</v>
+        <v>105.304</v>
       </c>
       <c r="F73">
-        <v>185.097</v>
+        <v>187.704</v>
       </c>
       <c r="G73">
         <v>48.4</v>
@@ -7267,37 +7267,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M73">
-        <v>43.64587260000001</v>
+        <v>44.26060320000001</v>
       </c>
       <c r="N73">
-        <v>-35.67920593333334</v>
+        <v>-36.29393653333334</v>
       </c>
       <c r="O73">
-        <v>-7.849425305333336</v>
+        <v>-7.984666037333335</v>
       </c>
       <c r="P73">
-        <v>-27.82978062800001</v>
+        <v>-28.30927049600001</v>
       </c>
       <c r="Q73">
-        <v>-20.87978062800001</v>
+        <v>-21.35927049600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1858314896587303</v>
+        <v>0.1908326142893993</v>
       </c>
       <c r="T73">
-        <v>3.233983594889846</v>
+        <v>3.349483008993055</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04015652711836643</v>
+        <v>0.03959879757505578</v>
       </c>
       <c r="W73">
-        <v>0.2263310909054892</v>
+        <v>0.2264626035318019</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1825296687198474</v>
+        <v>0.1799945344320718</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2164862065439291</v>
+        <v>0.2183862065439291</v>
       </c>
       <c r="C74">
-        <v>-91.97529422139094</v>
+        <v>-95.10333551883939</v>
       </c>
       <c r="D74">
-        <v>47.3287057786091</v>
+        <v>46.80766448116065</v>
       </c>
       <c r="E74">
-        <v>105.304</v>
+        <v>107.911</v>
       </c>
       <c r="F74">
-        <v>187.704</v>
+        <v>190.311</v>
       </c>
       <c r="G74">
         <v>48.4</v>
@@ -7349,37 +7349,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M74">
-        <v>44.26060320000001</v>
+        <v>44.87533380000001</v>
       </c>
       <c r="N74">
-        <v>-36.29393653333334</v>
+        <v>-36.90866713333334</v>
       </c>
       <c r="O74">
-        <v>-7.984666037333335</v>
+        <v>-8.119906769333335</v>
       </c>
       <c r="P74">
-        <v>-28.30927049600001</v>
+        <v>-28.78876036400001</v>
       </c>
       <c r="Q74">
-        <v>-21.35927049600001</v>
+        <v>-21.83876036400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1908326142893993</v>
+        <v>0.196204192596414</v>
       </c>
       <c r="T74">
-        <v>3.349483008993055</v>
+        <v>3.473537935252056</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03959879757505578</v>
+        <v>0.0390563482932057</v>
       </c>
       <c r="W74">
-        <v>0.2264626035318019</v>
+        <v>0.2265905130724621</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1799945344320718</v>
+        <v>0.1775288558782078</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2183862065439291</v>
+        <v>0.2202862065439292</v>
       </c>
       <c r="C75">
-        <v>-95.10333551883939</v>
+        <v>-98.22002946127614</v>
       </c>
       <c r="D75">
-        <v>46.80766448116065</v>
+        <v>46.2979705387239</v>
       </c>
       <c r="E75">
-        <v>107.911</v>
+        <v>110.518</v>
       </c>
       <c r="F75">
-        <v>190.311</v>
+        <v>192.918</v>
       </c>
       <c r="G75">
         <v>48.4</v>
@@ -7431,37 +7431,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M75">
-        <v>44.87533380000001</v>
+        <v>45.49006440000001</v>
       </c>
       <c r="N75">
-        <v>-36.90866713333334</v>
+        <v>-37.52339773333334</v>
       </c>
       <c r="O75">
-        <v>-8.119906769333335</v>
+        <v>-8.255147501333335</v>
       </c>
       <c r="P75">
-        <v>-28.78876036400001</v>
+        <v>-29.26825023200001</v>
       </c>
       <c r="Q75">
-        <v>-21.83876036400001</v>
+        <v>-22.31825023200001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.196204192596414</v>
+        <v>0.2019889692347377</v>
       </c>
       <c r="T75">
-        <v>3.473537935252056</v>
+        <v>3.607135548146366</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0390563482932057</v>
+        <v>0.03852855980275698</v>
       </c>
       <c r="W75">
-        <v>0.2265905130724621</v>
+        <v>0.2267149655985099</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1775288558782078</v>
+        <v>0.175129817285259</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2202862065439292</v>
+        <v>0.2221862065439291</v>
       </c>
       <c r="C76">
-        <v>-98.22002946127614</v>
+        <v>-101.3257427436079</v>
       </c>
       <c r="D76">
-        <v>46.2979705387239</v>
+        <v>45.79925725639212</v>
       </c>
       <c r="E76">
-        <v>110.518</v>
+        <v>113.125</v>
       </c>
       <c r="F76">
-        <v>192.918</v>
+        <v>195.525</v>
       </c>
       <c r="G76">
         <v>48.4</v>
@@ -7513,37 +7513,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M76">
-        <v>45.49006440000001</v>
+        <v>46.10479500000001</v>
       </c>
       <c r="N76">
-        <v>-37.52339773333334</v>
+        <v>-38.13812833333334</v>
       </c>
       <c r="O76">
-        <v>-8.255147501333335</v>
+        <v>-8.390388233333335</v>
       </c>
       <c r="P76">
-        <v>-29.26825023200001</v>
+        <v>-29.74774010000001</v>
       </c>
       <c r="Q76">
-        <v>-22.31825023200001</v>
+        <v>-22.79774010000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2019889692347377</v>
+        <v>0.2082365280041272</v>
       </c>
       <c r="T76">
-        <v>3.607135548146366</v>
+        <v>3.751420970072221</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03852855980275698</v>
+        <v>0.03801484567205355</v>
       </c>
       <c r="W76">
-        <v>0.2267149655985099</v>
+        <v>0.2268360993905298</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.175129817285259</v>
+        <v>0.1727947530547889</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2221862065439291</v>
+        <v>0.2240862065439291</v>
       </c>
       <c r="C77">
-        <v>-101.3257427436079</v>
+        <v>-104.420826429239</v>
       </c>
       <c r="D77">
-        <v>45.79925725639212</v>
+        <v>45.31117357076104</v>
       </c>
       <c r="E77">
-        <v>113.125</v>
+        <v>115.732</v>
       </c>
       <c r="F77">
-        <v>195.525</v>
+        <v>198.132</v>
       </c>
       <c r="G77">
         <v>48.4</v>
@@ -7595,37 +7595,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M77">
-        <v>46.10479500000001</v>
+        <v>46.71952560000001</v>
       </c>
       <c r="N77">
-        <v>-38.13812833333334</v>
+        <v>-38.75285893333334</v>
       </c>
       <c r="O77">
-        <v>-8.390388233333335</v>
+        <v>-8.525628965333336</v>
       </c>
       <c r="P77">
-        <v>-29.74774010000001</v>
+        <v>-30.22722996800001</v>
       </c>
       <c r="Q77">
-        <v>-22.79774010000001</v>
+        <v>-23.27722996800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2082365280041272</v>
+        <v>0.2150047166709659</v>
       </c>
       <c r="T77">
-        <v>3.751420970072221</v>
+        <v>3.907730177158565</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03801484567205355</v>
+        <v>0.03751465033426337</v>
       </c>
       <c r="W77">
-        <v>0.2268360993905298</v>
+        <v>0.2269540454511807</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1727947530547889</v>
+        <v>0.1705211378830154</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2240862065439291</v>
+        <v>0.2259862065439291</v>
       </c>
       <c r="C78">
-        <v>-104.420826429239</v>
+        <v>-107.5056167742145</v>
       </c>
       <c r="D78">
-        <v>45.31117357076104</v>
+        <v>44.83338322578557</v>
       </c>
       <c r="E78">
-        <v>115.732</v>
+        <v>118.339</v>
       </c>
       <c r="F78">
-        <v>198.132</v>
+        <v>200.739</v>
       </c>
       <c r="G78">
         <v>48.4</v>
@@ -7677,37 +7677,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M78">
-        <v>46.71952560000001</v>
+        <v>47.33425620000001</v>
       </c>
       <c r="N78">
-        <v>-38.75285893333334</v>
+        <v>-39.36758953333334</v>
       </c>
       <c r="O78">
-        <v>-8.525628965333336</v>
+        <v>-8.660869697333336</v>
       </c>
       <c r="P78">
-        <v>-30.22722996800001</v>
+        <v>-30.70671983600001</v>
       </c>
       <c r="Q78">
-        <v>-23.27722996800001</v>
+        <v>-23.75671983600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2150047166709659</v>
+        <v>0.2223614434827469</v>
       </c>
       <c r="T78">
-        <v>3.907730177158565</v>
+        <v>4.077631489208937</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03751465033426337</v>
+        <v>0.03702744708316904</v>
       </c>
       <c r="W78">
-        <v>0.2269540454511807</v>
+        <v>0.2270689279777887</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1705211378830154</v>
+        <v>0.1683065776507684</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2259862065439291</v>
+        <v>0.2278862065439292</v>
       </c>
       <c r="C79">
-        <v>-107.5056167742145</v>
+        <v>-110.580435999766</v>
       </c>
       <c r="D79">
-        <v>44.83338322578557</v>
+        <v>44.36556400023405</v>
       </c>
       <c r="E79">
-        <v>118.339</v>
+        <v>120.946</v>
       </c>
       <c r="F79">
-        <v>200.739</v>
+        <v>203.346</v>
       </c>
       <c r="G79">
         <v>48.4</v>
@@ -7759,37 +7759,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M79">
-        <v>47.33425620000001</v>
+        <v>47.94898680000001</v>
       </c>
       <c r="N79">
-        <v>-39.36758953333334</v>
+        <v>-39.98232013333334</v>
       </c>
       <c r="O79">
-        <v>-8.660869697333336</v>
+        <v>-8.796110429333334</v>
       </c>
       <c r="P79">
-        <v>-30.70671983600001</v>
+        <v>-31.18620970400001</v>
       </c>
       <c r="Q79">
-        <v>-23.75671983600001</v>
+        <v>-24.23620970400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2223614434827469</v>
+        <v>0.2303869636410536</v>
       </c>
       <c r="T79">
-        <v>4.077631489208937</v>
+        <v>4.26297837508207</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03702744708316904</v>
+        <v>0.03655273622312842</v>
       </c>
       <c r="W79">
-        <v>0.2270689279777887</v>
+        <v>0.2271808647985863</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1683065776507684</v>
+        <v>0.1661488010142201</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2278862065439292</v>
+        <v>0.2297862065439291</v>
       </c>
       <c r="C80">
-        <v>-110.580435999766</v>
+        <v>-113.6455930169895</v>
       </c>
       <c r="D80">
-        <v>44.36556400023405</v>
+        <v>43.9074069830105</v>
       </c>
       <c r="E80">
-        <v>120.946</v>
+        <v>123.553</v>
       </c>
       <c r="F80">
-        <v>203.346</v>
+        <v>205.953</v>
       </c>
       <c r="G80">
         <v>48.4</v>
@@ -7841,37 +7841,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M80">
-        <v>47.94898680000001</v>
+        <v>48.56371740000001</v>
       </c>
       <c r="N80">
-        <v>-39.98232013333334</v>
+        <v>-40.59705073333334</v>
       </c>
       <c r="O80">
-        <v>-8.796110429333334</v>
+        <v>-8.931351161333335</v>
       </c>
       <c r="P80">
-        <v>-31.18620970400001</v>
+        <v>-31.665699572</v>
       </c>
       <c r="Q80">
-        <v>-24.23620970400001</v>
+        <v>-24.71569957200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2303869636410536</v>
+        <v>0.2391768190525324</v>
       </c>
       <c r="T80">
-        <v>4.26297837508207</v>
+        <v>4.465977345324075</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03655273622312842</v>
+        <v>0.03609004335954451</v>
       </c>
       <c r="W80">
-        <v>0.2271808647985863</v>
+        <v>0.2272899677758194</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1661488010142201</v>
+        <v>0.1640456516342933</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2297862065439291</v>
+        <v>0.2316862065439291</v>
       </c>
       <c r="C81">
-        <v>-113.6455930169895</v>
+        <v>-116.7013841070805</v>
       </c>
       <c r="D81">
-        <v>43.9074069830105</v>
+        <v>43.45861589291957</v>
       </c>
       <c r="E81">
-        <v>123.553</v>
+        <v>126.1600000000001</v>
       </c>
       <c r="F81">
-        <v>205.953</v>
+        <v>208.5600000000001</v>
       </c>
       <c r="G81">
         <v>48.4</v>
@@ -7923,37 +7923,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M81">
-        <v>48.56371740000001</v>
+        <v>49.17844800000002</v>
       </c>
       <c r="N81">
-        <v>-40.59705073333334</v>
+        <v>-41.21178133333335</v>
       </c>
       <c r="O81">
-        <v>-8.931351161333335</v>
+        <v>-9.066591893333337</v>
       </c>
       <c r="P81">
-        <v>-31.665699572</v>
+        <v>-32.14518944000001</v>
       </c>
       <c r="Q81">
-        <v>-24.71569957200001</v>
+        <v>-25.19518944000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2391768190525324</v>
+        <v>0.248845660005159</v>
       </c>
       <c r="T81">
-        <v>4.465977345324075</v>
+        <v>4.689276212590277</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03609004335954451</v>
+        <v>0.0356389178175502</v>
       </c>
       <c r="W81">
-        <v>0.2272899677758194</v>
+        <v>0.2273963431786217</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1640456516342933</v>
+        <v>0.1619950809888646</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2316862065439291</v>
+        <v>0.2335862065439291</v>
       </c>
       <c r="C82">
-        <v>-116.7013841070805</v>
+        <v>-119.7480935602731</v>
       </c>
       <c r="D82">
-        <v>43.45861589291957</v>
+        <v>43.01890643972694</v>
       </c>
       <c r="E82">
-        <v>126.1600000000001</v>
+        <v>128.7670000000001</v>
       </c>
       <c r="F82">
-        <v>208.5600000000001</v>
+        <v>211.1670000000001</v>
       </c>
       <c r="G82">
         <v>48.4</v>
@@ -8005,37 +8005,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M82">
-        <v>49.17844800000002</v>
+        <v>49.79317860000002</v>
       </c>
       <c r="N82">
-        <v>-41.21178133333335</v>
+        <v>-41.82651193333335</v>
       </c>
       <c r="O82">
-        <v>-9.066591893333337</v>
+        <v>-9.201832625333337</v>
       </c>
       <c r="P82">
-        <v>-32.14518944000001</v>
+        <v>-32.62467930800001</v>
       </c>
       <c r="Q82">
-        <v>-25.19518944000001</v>
+        <v>-25.67467930800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.248845660005159</v>
+        <v>0.2595322736896411</v>
       </c>
       <c r="T82">
-        <v>4.689276212590277</v>
+        <v>4.93608022377924</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0356389178175502</v>
+        <v>0.03519893117782735</v>
       </c>
       <c r="W82">
-        <v>0.2273963431786217</v>
+        <v>0.2275000920282683</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1619950809888646</v>
+        <v>0.1599951417173971</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2335862065439291</v>
+        <v>0.2354862065439292</v>
       </c>
       <c r="C83">
-        <v>-119.7480935602731</v>
+        <v>-122.7859942763806</v>
       </c>
       <c r="D83">
-        <v>43.01890643972694</v>
+        <v>42.58800572361949</v>
       </c>
       <c r="E83">
-        <v>128.7670000000001</v>
+        <v>131.3740000000001</v>
       </c>
       <c r="F83">
-        <v>211.1670000000001</v>
+        <v>213.7740000000001</v>
       </c>
       <c r="G83">
         <v>48.4</v>
@@ -8087,37 +8087,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M83">
-        <v>49.79317860000002</v>
+        <v>50.40790920000001</v>
       </c>
       <c r="N83">
-        <v>-41.82651193333335</v>
+        <v>-42.44124253333334</v>
       </c>
       <c r="O83">
-        <v>-9.201832625333337</v>
+        <v>-9.337073357333336</v>
       </c>
       <c r="P83">
-        <v>-32.62467930800001</v>
+        <v>-33.10416917600001</v>
       </c>
       <c r="Q83">
-        <v>-25.67467930800001</v>
+        <v>-26.15416917600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2595322736896411</v>
+        <v>0.2714062888946212</v>
       </c>
       <c r="T83">
-        <v>4.93608022377924</v>
+        <v>5.210306902878087</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03519893117782735</v>
+        <v>0.03476967591956117</v>
       </c>
       <c r="W83">
-        <v>0.2275000920282683</v>
+        <v>0.2276013104181675</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1599951417173971</v>
+        <v>0.1580439814525508</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2354862065439292</v>
+        <v>0.2373862065439291</v>
       </c>
       <c r="C84">
-        <v>-122.7859942763806</v>
+        <v>-125.8153483296006</v>
       </c>
       <c r="D84">
-        <v>42.58800572361949</v>
+        <v>42.16565167039947</v>
       </c>
       <c r="E84">
-        <v>131.3740000000001</v>
+        <v>133.9810000000001</v>
       </c>
       <c r="F84">
-        <v>213.7740000000001</v>
+        <v>216.3810000000001</v>
       </c>
       <c r="G84">
         <v>48.4</v>
@@ -8169,37 +8169,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M84">
-        <v>50.40790920000001</v>
+        <v>51.02263980000001</v>
       </c>
       <c r="N84">
-        <v>-42.44124253333334</v>
+        <v>-43.05597313333335</v>
       </c>
       <c r="O84">
-        <v>-9.337073357333336</v>
+        <v>-9.472314089333336</v>
       </c>
       <c r="P84">
-        <v>-33.10416917600001</v>
+        <v>-33.58365904400001</v>
       </c>
       <c r="Q84">
-        <v>-26.15416917600001</v>
+        <v>-26.63365904400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2714062888946212</v>
+        <v>0.284677247064893</v>
       </c>
       <c r="T84">
-        <v>5.210306902878087</v>
+        <v>5.516795544223857</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03476967591956117</v>
+        <v>0.03435076416149417</v>
       </c>
       <c r="W84">
-        <v>0.2276013104181675</v>
+        <v>0.2277000898107197</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1580439814525508</v>
+        <v>0.1561398370977009</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2373862065439291</v>
+        <v>0.2392862065439291</v>
       </c>
       <c r="C85">
-        <v>-125.8153483296006</v>
+        <v>-128.8364075000437</v>
       </c>
       <c r="D85">
-        <v>42.16565167039947</v>
+        <v>41.75159249995639</v>
       </c>
       <c r="E85">
-        <v>133.9810000000001</v>
+        <v>136.5880000000001</v>
       </c>
       <c r="F85">
-        <v>216.3810000000001</v>
+        <v>218.9880000000001</v>
       </c>
       <c r="G85">
         <v>48.4</v>
@@ -8251,37 +8251,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M85">
-        <v>51.02263980000001</v>
+        <v>51.63737040000002</v>
       </c>
       <c r="N85">
-        <v>-43.05597313333335</v>
+        <v>-43.67070373333335</v>
       </c>
       <c r="O85">
-        <v>-9.472314089333336</v>
+        <v>-9.607554821333336</v>
       </c>
       <c r="P85">
-        <v>-33.58365904400001</v>
+        <v>-34.06314891200001</v>
       </c>
       <c r="Q85">
-        <v>-26.63365904400001</v>
+        <v>-27.11314891200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.284677247064893</v>
+        <v>0.2996070750064488</v>
       </c>
       <c r="T85">
-        <v>5.516795544223857</v>
+        <v>5.861595265737849</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03435076416149417</v>
+        <v>0.03394182649290495</v>
       </c>
       <c r="W85">
-        <v>0.2277000898107197</v>
+        <v>0.227796517312973</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1561398370977009</v>
+        <v>0.1542810295132043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2392862065439291</v>
+        <v>0.2411862065439291</v>
       </c>
       <c r="C86">
-        <v>-128.8364075000436</v>
+        <v>-131.8494137742485</v>
       </c>
       <c r="D86">
-        <v>41.75159249995639</v>
+        <v>41.34558622575155</v>
       </c>
       <c r="E86">
-        <v>136.588</v>
+        <v>139.195</v>
       </c>
       <c r="F86">
-        <v>218.988</v>
+        <v>221.595</v>
       </c>
       <c r="G86">
         <v>48.4</v>
@@ -8333,37 +8333,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M86">
-        <v>51.63737040000001</v>
+        <v>52.25210100000001</v>
       </c>
       <c r="N86">
-        <v>-43.67070373333334</v>
+        <v>-44.28543433333334</v>
       </c>
       <c r="O86">
-        <v>-9.607554821333334</v>
+        <v>-9.742795553333336</v>
       </c>
       <c r="P86">
-        <v>-34.063148912</v>
+        <v>-34.54263878</v>
       </c>
       <c r="Q86">
-        <v>-27.113148912</v>
+        <v>-27.59263878000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2996070750064487</v>
+        <v>0.3165275466735453</v>
       </c>
       <c r="T86">
-        <v>5.861595265737845</v>
+        <v>6.252368283453702</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03394182649290496</v>
+        <v>0.03354251088710607</v>
       </c>
       <c r="W86">
-        <v>0.227796517312973</v>
+        <v>0.2278906759328204</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1542810295132044</v>
+        <v>0.1524659585777549</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2411862065439291</v>
+        <v>0.2430862065439292</v>
       </c>
       <c r="C87">
-        <v>-131.8494137742485</v>
+        <v>-134.8545998167756</v>
       </c>
       <c r="D87">
-        <v>41.34558622575155</v>
+        <v>40.94740018322437</v>
       </c>
       <c r="E87">
-        <v>139.195</v>
+        <v>141.802</v>
       </c>
       <c r="F87">
-        <v>221.595</v>
+        <v>224.202</v>
       </c>
       <c r="G87">
         <v>48.4</v>
@@ -8415,37 +8415,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M87">
-        <v>52.25210100000001</v>
+        <v>52.86683160000001</v>
       </c>
       <c r="N87">
-        <v>-44.28543433333334</v>
+        <v>-44.90016493333334</v>
       </c>
       <c r="O87">
-        <v>-9.742795553333336</v>
+        <v>-9.878036285333335</v>
       </c>
       <c r="P87">
-        <v>-34.54263878</v>
+        <v>-35.02212864800001</v>
       </c>
       <c r="Q87">
-        <v>-27.59263878000001</v>
+        <v>-28.07212864800001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3165275466735453</v>
+        <v>0.3358652285787985</v>
       </c>
       <c r="T87">
-        <v>6.252368283453702</v>
+        <v>6.698966017986109</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03354251088710607</v>
+        <v>0.03315248169074438</v>
       </c>
       <c r="W87">
-        <v>0.2278906759328204</v>
+        <v>0.2279826448173225</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1524659585777549</v>
+        <v>0.1506930985942927</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2430862065439292</v>
+        <v>0.2449862065439291</v>
       </c>
       <c r="C88">
-        <v>-134.8545998167756</v>
+        <v>-137.8521894148107</v>
       </c>
       <c r="D88">
-        <v>40.94740018322437</v>
+        <v>40.55681058518928</v>
       </c>
       <c r="E88">
-        <v>141.802</v>
+        <v>144.409</v>
       </c>
       <c r="F88">
-        <v>224.202</v>
+        <v>226.809</v>
       </c>
       <c r="G88">
         <v>48.4</v>
@@ -8497,37 +8497,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M88">
-        <v>52.86683160000001</v>
+        <v>53.48156220000001</v>
       </c>
       <c r="N88">
-        <v>-44.90016493333334</v>
+        <v>-45.51489553333334</v>
       </c>
       <c r="O88">
-        <v>-9.878036285333335</v>
+        <v>-10.01327701733334</v>
       </c>
       <c r="P88">
-        <v>-35.02212864800001</v>
+        <v>-35.501618516</v>
       </c>
       <c r="Q88">
-        <v>-28.07212864800001</v>
+        <v>-28.551618516</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3358652285787985</v>
+        <v>0.3581779384694753</v>
       </c>
       <c r="T88">
-        <v>6.698966017986109</v>
+        <v>7.214271096292733</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03315248169074438</v>
+        <v>0.03277141868280479</v>
       </c>
       <c r="W88">
-        <v>0.2279826448173225</v>
+        <v>0.2280724994745947</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1506930985942927</v>
+        <v>0.1489609940127491</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2449862065439291</v>
+        <v>0.2468862065439291</v>
       </c>
       <c r="C89">
-        <v>-137.8521894148107</v>
+        <v>-140.8423978975618</v>
       </c>
       <c r="D89">
-        <v>40.55681058518928</v>
+        <v>40.17360210243826</v>
       </c>
       <c r="E89">
-        <v>144.409</v>
+        <v>147.016</v>
       </c>
       <c r="F89">
-        <v>226.809</v>
+        <v>229.4160000000001</v>
       </c>
       <c r="G89">
         <v>48.4</v>
@@ -8579,37 +8579,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M89">
-        <v>53.48156220000001</v>
+        <v>54.09629280000001</v>
       </c>
       <c r="N89">
-        <v>-45.51489553333334</v>
+        <v>-46.12962613333335</v>
       </c>
       <c r="O89">
-        <v>-10.01327701733334</v>
+        <v>-10.14851774933334</v>
       </c>
       <c r="P89">
-        <v>-35.501618516</v>
+        <v>-35.98110838400001</v>
       </c>
       <c r="Q89">
-        <v>-28.551618516</v>
+        <v>-29.03110838400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3581779384694753</v>
+        <v>0.3842094333419316</v>
       </c>
       <c r="T89">
-        <v>7.214271096292733</v>
+        <v>7.815460354317127</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03277141868280479</v>
+        <v>0.03239901619777291</v>
       </c>
       <c r="W89">
-        <v>0.2280724994745947</v>
+        <v>0.2281603119805651</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1489609940127491</v>
+        <v>0.1472682554444223</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2468862065439291</v>
+        <v>0.2487862065439292</v>
       </c>
       <c r="C90">
-        <v>-140.8423978975618</v>
+        <v>-143.8254325321029</v>
       </c>
       <c r="D90">
-        <v>40.17360210243826</v>
+        <v>39.79756746789715</v>
       </c>
       <c r="E90">
-        <v>147.016</v>
+        <v>149.623</v>
       </c>
       <c r="F90">
-        <v>229.4160000000001</v>
+        <v>232.0230000000001</v>
       </c>
       <c r="G90">
         <v>48.4</v>
@@ -8661,37 +8661,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M90">
-        <v>54.09629280000001</v>
+        <v>54.71102340000002</v>
       </c>
       <c r="N90">
-        <v>-46.12962613333335</v>
+        <v>-46.74435673333335</v>
       </c>
       <c r="O90">
-        <v>-10.14851774933334</v>
+        <v>-10.28375848133334</v>
       </c>
       <c r="P90">
-        <v>-35.98110838400001</v>
+        <v>-36.46059825200001</v>
       </c>
       <c r="Q90">
-        <v>-29.03110838400001</v>
+        <v>-29.51059825200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3842094333419316</v>
+        <v>0.4149739272821072</v>
       </c>
       <c r="T90">
-        <v>7.815460354317127</v>
+        <v>8.52595675016414</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03239901619777291</v>
+        <v>0.03203498230791029</v>
       </c>
       <c r="W90">
-        <v>0.2281603119805651</v>
+        <v>0.2282461511717948</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1472682554444223</v>
+        <v>0.1456135559450469</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2487862065439292</v>
+        <v>0.2506862065439291</v>
       </c>
       <c r="C91">
-        <v>-143.8254325321029</v>
+        <v>-146.8014928971929</v>
       </c>
       <c r="D91">
-        <v>39.79756746789715</v>
+        <v>39.42850710280716</v>
       </c>
       <c r="E91">
-        <v>149.623</v>
+        <v>152.23</v>
       </c>
       <c r="F91">
-        <v>232.0230000000001</v>
+        <v>234.6300000000001</v>
       </c>
       <c r="G91">
         <v>48.4</v>
@@ -8743,37 +8743,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M91">
-        <v>54.71102340000002</v>
+        <v>55.32575400000002</v>
       </c>
       <c r="N91">
-        <v>-46.74435673333335</v>
+        <v>-47.35908733333335</v>
       </c>
       <c r="O91">
-        <v>-10.28375848133334</v>
+        <v>-10.41899921333334</v>
       </c>
       <c r="P91">
-        <v>-36.46059825200001</v>
+        <v>-36.94008812000001</v>
       </c>
       <c r="Q91">
-        <v>-29.51059825200001</v>
+        <v>-29.99008812000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4149739272821072</v>
+        <v>0.451891320010318</v>
       </c>
       <c r="T91">
-        <v>8.52595675016414</v>
+        <v>9.378552425180555</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03203498230791029</v>
+        <v>0.03167903806004462</v>
       </c>
       <c r="W91">
-        <v>0.2282461511717948</v>
+        <v>0.2283300828254415</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1456135559450469</v>
+        <v>0.1439956275456574</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2506862065439291</v>
+        <v>0.2525862065439292</v>
       </c>
       <c r="C92">
-        <v>-146.8014928971929</v>
+        <v>-149.7707712364854</v>
       </c>
       <c r="D92">
-        <v>39.42850710280716</v>
+        <v>39.06622876351465</v>
       </c>
       <c r="E92">
-        <v>152.23</v>
+        <v>154.837</v>
       </c>
       <c r="F92">
-        <v>234.6300000000001</v>
+        <v>237.2370000000001</v>
       </c>
       <c r="G92">
         <v>48.4</v>
@@ -8825,37 +8825,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M92">
-        <v>55.32575400000002</v>
+        <v>55.94048460000001</v>
       </c>
       <c r="N92">
-        <v>-47.35908733333335</v>
+        <v>-47.97381793333334</v>
       </c>
       <c r="O92">
-        <v>-10.41899921333334</v>
+        <v>-10.55423994533334</v>
       </c>
       <c r="P92">
-        <v>-36.94008812000001</v>
+        <v>-37.41957798800001</v>
       </c>
       <c r="Q92">
-        <v>-29.99008812000001</v>
+        <v>-30.46957798800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.451891320010318</v>
+        <v>0.4970125777892423</v>
       </c>
       <c r="T92">
-        <v>9.378552425180555</v>
+        <v>10.42061380575617</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03167903806004462</v>
+        <v>0.03133091676268149</v>
       </c>
       <c r="W92">
-        <v>0.2283300828254415</v>
+        <v>0.2284121698273597</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1439956275456574</v>
+        <v>0.1424132580121886</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2525862065439292</v>
+        <v>0.2544862065439291</v>
       </c>
       <c r="C93">
-        <v>-149.7707712364854</v>
+        <v>-152.7334527924442</v>
       </c>
       <c r="D93">
-        <v>39.06622876351465</v>
+        <v>38.71054720755589</v>
       </c>
       <c r="E93">
-        <v>154.837</v>
+        <v>157.444</v>
       </c>
       <c r="F93">
-        <v>237.2370000000001</v>
+        <v>239.8440000000001</v>
       </c>
       <c r="G93">
         <v>48.4</v>
@@ -8907,37 +8907,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M93">
-        <v>55.94048460000001</v>
+        <v>56.55521520000001</v>
       </c>
       <c r="N93">
-        <v>-47.97381793333334</v>
+        <v>-48.58854853333334</v>
       </c>
       <c r="O93">
-        <v>-10.55423994533334</v>
+        <v>-10.68948067733334</v>
       </c>
       <c r="P93">
-        <v>-37.41957798800001</v>
+        <v>-37.89906785600001</v>
       </c>
       <c r="Q93">
-        <v>-30.46957798800001</v>
+        <v>-30.94906785600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4970125777892423</v>
+        <v>0.5534141500128976</v>
       </c>
       <c r="T93">
-        <v>10.42061380575617</v>
+        <v>11.7231905314757</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03133091676268149</v>
+        <v>0.03099036331960887</v>
       </c>
       <c r="W93">
-        <v>0.2284121698273597</v>
+        <v>0.2284924723292362</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1424132580121886</v>
+        <v>0.1408652878164041</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2544862065439291</v>
+        <v>0.2563862065439292</v>
       </c>
       <c r="C94">
-        <v>-152.7334527924442</v>
+        <v>-155.6897161221819</v>
       </c>
       <c r="D94">
-        <v>38.71054720755589</v>
+        <v>38.3612838778182</v>
       </c>
       <c r="E94">
-        <v>157.444</v>
+        <v>160.051</v>
       </c>
       <c r="F94">
-        <v>239.8440000000001</v>
+        <v>242.4510000000001</v>
       </c>
       <c r="G94">
         <v>48.4</v>
@@ -8989,37 +8989,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M94">
-        <v>56.55521520000001</v>
+        <v>57.16994580000001</v>
       </c>
       <c r="N94">
-        <v>-48.58854853333334</v>
+        <v>-49.20327913333335</v>
       </c>
       <c r="O94">
-        <v>-10.68948067733334</v>
+        <v>-10.82472140933334</v>
       </c>
       <c r="P94">
-        <v>-37.89906785600001</v>
+        <v>-38.37855772400001</v>
       </c>
       <c r="Q94">
-        <v>-30.94906785600001</v>
+        <v>-31.42855772400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5534141500128976</v>
+        <v>0.6259304571575974</v>
       </c>
       <c r="T94">
-        <v>11.7231905314757</v>
+        <v>13.39793203597223</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03099036331960887</v>
+        <v>0.03065713360649479</v>
       </c>
       <c r="W94">
-        <v>0.2284924723292362</v>
+        <v>0.2285710478955885</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1408652878164041</v>
+        <v>0.1393506073022491</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2563862065439292</v>
+        <v>0.2582862065439291</v>
       </c>
       <c r="C95">
-        <v>-155.6897161221819</v>
+        <v>-158.6397333963539</v>
       </c>
       <c r="D95">
-        <v>38.3612838778182</v>
+        <v>38.01826660364617</v>
       </c>
       <c r="E95">
-        <v>160.051</v>
+        <v>162.658</v>
       </c>
       <c r="F95">
-        <v>242.4510000000001</v>
+        <v>245.058</v>
       </c>
       <c r="G95">
         <v>48.4</v>
@@ -9071,37 +9071,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M95">
-        <v>57.16994580000001</v>
+        <v>57.78467640000002</v>
       </c>
       <c r="N95">
-        <v>-49.20327913333335</v>
+        <v>-49.81800973333335</v>
       </c>
       <c r="O95">
-        <v>-10.82472140933334</v>
+        <v>-10.95996214133334</v>
       </c>
       <c r="P95">
-        <v>-38.37855772400001</v>
+        <v>-38.85804759200001</v>
       </c>
       <c r="Q95">
-        <v>-31.42855772400001</v>
+        <v>-31.90804759200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6259304571575974</v>
+        <v>0.7226188666838638</v>
       </c>
       <c r="T95">
-        <v>13.39793203597223</v>
+        <v>15.63092070863427</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03065713360649479</v>
+        <v>0.03033099388727676</v>
       </c>
       <c r="W95">
-        <v>0.2285710478955885</v>
+        <v>0.2286479516413801</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1393506073022491</v>
+        <v>0.1378681540330763</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2582862065439291</v>
+        <v>0.2601862065439292</v>
       </c>
       <c r="C96">
-        <v>-158.6397333963539</v>
+        <v>-161.5836706821588</v>
       </c>
       <c r="D96">
-        <v>38.01826660364617</v>
+        <v>37.68132931784124</v>
       </c>
       <c r="E96">
-        <v>162.658</v>
+        <v>165.265</v>
       </c>
       <c r="F96">
-        <v>245.058</v>
+        <v>247.665</v>
       </c>
       <c r="G96">
         <v>48.4</v>
@@ -9153,37 +9153,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M96">
-        <v>57.78467640000002</v>
+        <v>58.39940700000001</v>
       </c>
       <c r="N96">
-        <v>-49.81800973333335</v>
+        <v>-50.43274033333334</v>
       </c>
       <c r="O96">
-        <v>-10.95996214133334</v>
+        <v>-11.09520287333333</v>
       </c>
       <c r="P96">
-        <v>-38.85804759200001</v>
+        <v>-39.33753746000001</v>
       </c>
       <c r="Q96">
-        <v>-31.90804759200001</v>
+        <v>-32.38753746</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7226188666838638</v>
+        <v>0.8579826400206371</v>
       </c>
       <c r="T96">
-        <v>15.63092070863427</v>
+        <v>18.75710485036113</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03033099388727676</v>
+        <v>0.0300117202674107</v>
       </c>
       <c r="W96">
-        <v>0.2286479516413801</v>
+        <v>0.2287232363609445</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1378681540330763</v>
+        <v>0.1364169103064123</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2601862065439292</v>
+        <v>0.2620862065439292</v>
       </c>
       <c r="C97">
-        <v>-161.5836706821588</v>
+        <v>-164.5216882114221</v>
       </c>
       <c r="D97">
-        <v>37.68132931784124</v>
+        <v>37.35031178857796</v>
       </c>
       <c r="E97">
-        <v>165.265</v>
+        <v>167.8720000000001</v>
       </c>
       <c r="F97">
-        <v>247.665</v>
+        <v>250.2720000000001</v>
       </c>
       <c r="G97">
         <v>48.4</v>
@@ -9235,37 +9235,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M97">
-        <v>58.39940700000001</v>
+        <v>59.01413760000002</v>
       </c>
       <c r="N97">
-        <v>-50.43274033333334</v>
+        <v>-51.04747093333335</v>
       </c>
       <c r="O97">
-        <v>-11.09520287333333</v>
+        <v>-11.23044360533334</v>
       </c>
       <c r="P97">
-        <v>-39.33753746000001</v>
+        <v>-39.81702732800002</v>
       </c>
       <c r="Q97">
-        <v>-32.38753746</v>
+        <v>-32.86702732800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8579826400206371</v>
+        <v>1.061028300025797</v>
       </c>
       <c r="T97">
-        <v>18.75710485036113</v>
+        <v>23.44638106295143</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0300117202674107</v>
+        <v>0.02969909818129183</v>
       </c>
       <c r="W97">
-        <v>0.2287232363609445</v>
+        <v>0.2287969526488514</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1364169103064123</v>
+        <v>0.1349959008240539</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2620862065439292</v>
+        <v>0.2639862065439291</v>
       </c>
       <c r="C98">
-        <v>-164.5216882114221</v>
+        <v>-167.4539406346728</v>
       </c>
       <c r="D98">
-        <v>37.35031178857796</v>
+        <v>37.02505936532722</v>
       </c>
       <c r="E98">
-        <v>167.872</v>
+        <v>170.479</v>
       </c>
       <c r="F98">
-        <v>250.272</v>
+        <v>252.879</v>
       </c>
       <c r="G98">
         <v>48.4</v>
@@ -9317,37 +9317,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M98">
-        <v>59.01413760000001</v>
+        <v>59.62886820000001</v>
       </c>
       <c r="N98">
-        <v>-51.04747093333334</v>
+        <v>-51.66220153333335</v>
       </c>
       <c r="O98">
-        <v>-11.23044360533334</v>
+        <v>-11.36568433733334</v>
       </c>
       <c r="P98">
-        <v>-39.81702732800001</v>
+        <v>-40.29651719600001</v>
       </c>
       <c r="Q98">
-        <v>-32.86702732800001</v>
+        <v>-33.34651719600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.061028300025794</v>
+        <v>1.399437733367725</v>
       </c>
       <c r="T98">
-        <v>23.44638106295136</v>
+        <v>31.26184141726849</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02969909818129184</v>
+        <v>0.02939292191138161</v>
       </c>
       <c r="W98">
-        <v>0.2287969526488514</v>
+        <v>0.2288691490132962</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1349959008240539</v>
+        <v>0.1336041905062801</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2639862065439291</v>
+        <v>0.2658862065439291</v>
       </c>
       <c r="C99">
-        <v>-167.4539406346728</v>
+        <v>-170.3805772620599</v>
       </c>
       <c r="D99">
-        <v>37.02505936532722</v>
+        <v>36.70542273794013</v>
       </c>
       <c r="E99">
-        <v>170.479</v>
+        <v>173.086</v>
       </c>
       <c r="F99">
-        <v>252.879</v>
+        <v>255.486</v>
       </c>
       <c r="G99">
         <v>48.4</v>
@@ -9399,37 +9399,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M99">
-        <v>59.62886820000001</v>
+        <v>60.24359880000002</v>
       </c>
       <c r="N99">
-        <v>-51.66220153333335</v>
+        <v>-52.27693213333335</v>
       </c>
       <c r="O99">
-        <v>-11.36568433733334</v>
+        <v>-11.50092506933334</v>
       </c>
       <c r="P99">
-        <v>-40.29651719600001</v>
+        <v>-40.77600706400001</v>
       </c>
       <c r="Q99">
-        <v>-33.34651719600001</v>
+        <v>-33.82600706400001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.399437733367725</v>
+        <v>2.076256600051588</v>
       </c>
       <c r="T99">
-        <v>31.26184141726849</v>
+        <v>46.89276212590273</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02939292191138161</v>
+        <v>0.02909299413677567</v>
       </c>
       <c r="W99">
-        <v>0.2288691490132962</v>
+        <v>0.2289398719825483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1336041905062801</v>
+        <v>0.1322408824398895</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2658862065439291</v>
+        <v>0.2677862065439292</v>
       </c>
       <c r="C100">
-        <v>-170.3805772620599</v>
+        <v>-173.301742291896</v>
       </c>
       <c r="D100">
-        <v>36.70542273794013</v>
+        <v>36.39125770810399</v>
       </c>
       <c r="E100">
-        <v>173.086</v>
+        <v>175.693</v>
       </c>
       <c r="F100">
-        <v>255.486</v>
+        <v>258.093</v>
       </c>
       <c r="G100">
         <v>48.4</v>
@@ -9481,37 +9481,37 @@
         <v>7.966666666666666</v>
       </c>
       <c r="M100">
-        <v>60.24359880000002</v>
+        <v>60.85832940000001</v>
       </c>
       <c r="N100">
-        <v>-52.27693213333335</v>
+        <v>-52.89166273333334</v>
       </c>
       <c r="O100">
-        <v>-11.50092506933334</v>
+        <v>-11.63616580133334</v>
       </c>
       <c r="P100">
-        <v>-40.77600706400001</v>
+        <v>-41.25549693200001</v>
       </c>
       <c r="Q100">
-        <v>-33.82600706400001</v>
+        <v>-34.305496932</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.076256600051588</v>
+        <v>4.106713200103176</v>
       </c>
       <c r="T100">
-        <v>46.89276212590273</v>
+        <v>93.78552425180546</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02909299413677567</v>
+        <v>0.02879912550913147</v>
       </c>
       <c r="W100">
-        <v>0.2289398719825483</v>
+        <v>0.2290091662049468</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1322408824398895</v>
+        <v>0.1309051159505977</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2677862065439292</v>
-      </c>
-      <c r="C101">
-        <v>-173.301742291896</v>
-      </c>
-      <c r="D101">
-        <v>36.39125770810399</v>
-      </c>
-      <c r="E101">
-        <v>175.693</v>
-      </c>
-      <c r="F101">
-        <v>258.093</v>
-      </c>
-      <c r="G101">
-        <v>48.4</v>
-      </c>
-      <c r="H101">
-        <v>178.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.91666666666667</v>
-      </c>
-      <c r="K101">
-        <v>6.95</v>
-      </c>
-      <c r="L101">
-        <v>7.966666666666666</v>
-      </c>
-      <c r="M101">
-        <v>60.85832940000001</v>
-      </c>
-      <c r="N101">
-        <v>-52.89166273333334</v>
-      </c>
-      <c r="O101">
-        <v>-11.63616580133334</v>
-      </c>
-      <c r="P101">
-        <v>-41.25549693200001</v>
-      </c>
-      <c r="Q101">
-        <v>-34.305496932</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.106713200103176</v>
-      </c>
-      <c r="T101">
-        <v>93.78552425180546</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02879912550913147</v>
-      </c>
-      <c r="W101">
-        <v>0.2290091662049468</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1309051159505977</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
